--- a/Docs/Assets_Template_ updated final.xlsx
+++ b/Docs/Assets_Template_ updated final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\logistic\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59607F5-8F57-48E0-ADB7-4100C04AE11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8AA5BC-4841-4356-A949-0ADAC30C9629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="769" activeTab="6" xr2:uid="{CB6DDDD5-16B0-448E-8171-F32A2B4AEEC5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="769" activeTab="6" xr2:uid="{CB6DDDD5-16B0-448E-8171-F32A2B4AEEC5}"/>
   </bookViews>
   <sheets>
     <sheet name="suppliers" sheetId="7" r:id="rId1"/>
@@ -222,7 +222,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4621" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4622" uniqueCount="801">
   <si>
     <t>Furniture categories</t>
   </si>
@@ -2622,6 +2622,9 @@
   </si>
   <si>
     <t>Vehicles_sub categories</t>
+  </si>
+  <si>
+    <t>owned_by</t>
   </si>
 </sst>
 </file>
@@ -3301,28 +3304,10 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3333,6 +3318,24 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3702,10 +3705,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ED3D666-6F89-4C9E-98EB-D035BF17A680}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B198"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="3.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="47.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3716,7 +3719,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15">
+    <row r="2" spans="1:2" ht="14.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3724,7 +3727,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15">
+    <row r="3" spans="1:2" ht="14.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3756,7 +3759,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15">
+    <row r="7" spans="1:2" ht="14.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3764,7 +3767,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15">
+    <row r="8" spans="1:2" ht="14.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3772,7 +3775,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15">
+    <row r="9" spans="1:2" ht="14.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3796,7 +3799,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15">
+    <row r="12" spans="1:2" ht="14.4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3804,7 +3807,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15">
+    <row r="13" spans="1:2" ht="14.4">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3820,7 +3823,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15">
+    <row r="15" spans="1:2" ht="14.4">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3828,7 +3831,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15">
+    <row r="16" spans="1:2" ht="14.4">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3836,7 +3839,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15">
+    <row r="17" spans="1:2" ht="14.4">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3844,7 +3847,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15">
+    <row r="18" spans="1:2" ht="14.4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3852,7 +3855,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15">
+    <row r="19" spans="1:2" ht="14.4">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3860,7 +3863,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15">
+    <row r="20" spans="1:2" ht="14.4">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3868,7 +3871,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15">
+    <row r="21" spans="1:2" ht="14.4">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3876,7 +3879,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15">
+    <row r="22" spans="1:2" ht="14.4">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3884,7 +3887,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15">
+    <row r="23" spans="1:2" ht="14.4">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3892,7 +3895,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15">
+    <row r="24" spans="1:2" ht="14.4">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3900,7 +3903,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75">
+    <row r="25" spans="1:2" ht="15.6">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3908,7 +3911,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15">
+    <row r="26" spans="1:2" ht="14.4">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3916,7 +3919,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15">
+    <row r="27" spans="1:2" ht="14.4">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3924,7 +3927,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15">
+    <row r="28" spans="1:2" ht="14.4">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3932,7 +3935,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15">
+    <row r="29" spans="1:2" ht="14.4">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3948,7 +3951,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15">
+    <row r="31" spans="1:2" ht="14.4">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3964,7 +3967,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75">
+    <row r="33" spans="1:2" ht="15.6">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3972,7 +3975,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15">
+    <row r="34" spans="1:2" ht="14.4">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3980,7 +3983,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15">
+    <row r="35" spans="1:2" ht="14.4">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3988,7 +3991,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15">
+    <row r="36" spans="1:2" ht="14.4">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3996,7 +3999,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15">
+    <row r="37" spans="1:2" ht="14.4">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4004,7 +4007,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15">
+    <row r="38" spans="1:2" ht="14.4">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4012,7 +4015,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15">
+    <row r="39" spans="1:2" ht="14.4">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4020,7 +4023,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15">
+    <row r="40" spans="1:2" ht="14.4">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4028,7 +4031,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15">
+    <row r="41" spans="1:2" ht="14.4">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4164,7 +4167,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15">
+    <row r="58" spans="1:2" ht="14.4">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4180,7 +4183,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15">
+    <row r="60" spans="1:2" ht="14.4">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4188,7 +4191,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15">
+    <row r="61" spans="1:2" ht="14.4">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4196,7 +4199,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15">
+    <row r="62" spans="1:2" ht="14.4">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4204,7 +4207,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15">
+    <row r="63" spans="1:2" ht="14.4">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4212,7 +4215,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15">
+    <row r="64" spans="1:2" ht="14.4">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4220,7 +4223,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15">
+    <row r="65" spans="1:2" ht="14.4">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4228,7 +4231,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15">
+    <row r="66" spans="1:2" ht="14.4">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4236,7 +4239,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15">
+    <row r="67" spans="1:2" ht="14.4">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4244,7 +4247,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15">
+    <row r="68" spans="1:2" ht="14.4">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4252,7 +4255,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15">
+    <row r="69" spans="1:2" ht="14.4">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4260,7 +4263,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15">
+    <row r="70" spans="1:2" ht="14.4">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4268,7 +4271,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75">
+    <row r="71" spans="1:2" ht="15.6">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4276,7 +4279,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.75">
+    <row r="72" spans="1:2" ht="15.6">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4284,7 +4287,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15.75">
+    <row r="73" spans="1:2" ht="15.6">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4292,7 +4295,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75">
+    <row r="74" spans="1:2" ht="15.6">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4324,7 +4327,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75">
+    <row r="78" spans="1:2" ht="15.6">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4356,7 +4359,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15">
+    <row r="82" spans="1:2" ht="14.4">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4388,7 +4391,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15">
+    <row r="86" spans="1:2" ht="14.4">
       <c r="A86">
         <v>85</v>
       </c>
@@ -4468,7 +4471,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15">
+    <row r="96" spans="1:2" ht="14.4">
       <c r="A96">
         <v>95</v>
       </c>
@@ -4476,7 +4479,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15">
+    <row r="97" spans="1:2" ht="14.4">
       <c r="A97">
         <v>96</v>
       </c>
@@ -4484,7 +4487,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15">
+    <row r="98" spans="1:2" ht="14.4">
       <c r="A98">
         <v>97</v>
       </c>
@@ -4492,7 +4495,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15">
+    <row r="99" spans="1:2" ht="14.4">
       <c r="A99">
         <v>98</v>
       </c>
@@ -4500,7 +4503,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15">
+    <row r="100" spans="1:2" ht="14.4">
       <c r="A100">
         <v>99</v>
       </c>
@@ -4508,7 +4511,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15">
+    <row r="101" spans="1:2" ht="14.4">
       <c r="A101">
         <v>100</v>
       </c>
@@ -4516,7 +4519,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15">
+    <row r="102" spans="1:2" ht="14.4">
       <c r="A102">
         <v>101</v>
       </c>
@@ -4532,7 +4535,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15">
+    <row r="104" spans="1:2" ht="14.4">
       <c r="A104">
         <v>103</v>
       </c>
@@ -4612,7 +4615,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15">
+    <row r="114" spans="1:2" ht="14.4">
       <c r="A114">
         <v>113</v>
       </c>
@@ -4620,7 +4623,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="15">
+    <row r="115" spans="1:2" ht="14.4">
       <c r="A115">
         <v>114</v>
       </c>
@@ -4628,7 +4631,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="15">
+    <row r="116" spans="1:2" ht="14.4">
       <c r="A116">
         <v>115</v>
       </c>
@@ -4636,7 +4639,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="15">
+    <row r="117" spans="1:2" ht="14.4">
       <c r="A117">
         <v>116</v>
       </c>
@@ -4644,7 +4647,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="15">
+    <row r="118" spans="1:2" ht="14.4">
       <c r="A118">
         <v>117</v>
       </c>
@@ -4652,7 +4655,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="15">
+    <row r="119" spans="1:2" ht="14.4">
       <c r="A119">
         <v>118</v>
       </c>
@@ -4660,7 +4663,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="15">
+    <row r="120" spans="1:2" ht="14.4">
       <c r="A120">
         <v>119</v>
       </c>
@@ -4668,7 +4671,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="15">
+    <row r="121" spans="1:2" ht="14.4">
       <c r="A121">
         <v>120</v>
       </c>
@@ -4676,7 +4679,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="15">
+    <row r="122" spans="1:2" ht="14.4">
       <c r="A122">
         <v>121</v>
       </c>
@@ -4708,7 +4711,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="15">
+    <row r="126" spans="1:2" ht="14.4">
       <c r="A126">
         <v>125</v>
       </c>
@@ -4716,7 +4719,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="15">
+    <row r="127" spans="1:2" ht="14.4">
       <c r="A127">
         <v>126</v>
       </c>
@@ -4724,7 +4727,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="15">
+    <row r="128" spans="1:2" ht="14.4">
       <c r="A128">
         <v>127</v>
       </c>
@@ -4732,7 +4735,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="15">
+    <row r="129" spans="1:2" ht="14.4">
       <c r="A129">
         <v>128</v>
       </c>
@@ -4740,7 +4743,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="15">
+    <row r="130" spans="1:2" ht="14.4">
       <c r="A130">
         <v>129</v>
       </c>
@@ -4748,7 +4751,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="15">
+    <row r="131" spans="1:2" ht="14.4">
       <c r="A131">
         <v>130</v>
       </c>
@@ -4756,7 +4759,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="15">
+    <row r="132" spans="1:2" ht="14.4">
       <c r="A132">
         <v>131</v>
       </c>
@@ -4764,7 +4767,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="15">
+    <row r="133" spans="1:2" ht="14.4">
       <c r="A133">
         <v>132</v>
       </c>
@@ -4772,7 +4775,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="15">
+    <row r="134" spans="1:2" ht="14.4">
       <c r="A134">
         <v>133</v>
       </c>
@@ -4780,7 +4783,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="15">
+    <row r="135" spans="1:2" ht="14.4">
       <c r="A135">
         <v>134</v>
       </c>
@@ -4788,7 +4791,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="15">
+    <row r="136" spans="1:2" ht="14.4">
       <c r="A136">
         <v>135</v>
       </c>
@@ -4796,7 +4799,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="15">
+    <row r="137" spans="1:2" ht="14.4">
       <c r="A137">
         <v>136</v>
       </c>
@@ -4804,7 +4807,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="15">
+    <row r="138" spans="1:2" ht="14.4">
       <c r="A138">
         <v>137</v>
       </c>
@@ -4812,7 +4815,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="15">
+    <row r="139" spans="1:2" ht="14.4">
       <c r="A139">
         <v>138</v>
       </c>
@@ -4820,7 +4823,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="15">
+    <row r="140" spans="1:2" ht="14.4">
       <c r="A140">
         <v>139</v>
       </c>
@@ -4828,7 +4831,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="15">
+    <row r="141" spans="1:2" ht="14.4">
       <c r="A141">
         <v>140</v>
       </c>
@@ -4836,7 +4839,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="15">
+    <row r="142" spans="1:2" ht="14.4">
       <c r="A142">
         <v>141</v>
       </c>
@@ -4844,7 +4847,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="143" spans="1:2" ht="15">
+    <row r="143" spans="1:2" ht="14.4">
       <c r="A143">
         <v>142</v>
       </c>
@@ -4852,7 +4855,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="144" spans="1:2" ht="15">
+    <row r="144" spans="1:2" ht="14.4">
       <c r="A144">
         <v>143</v>
       </c>
@@ -4860,7 +4863,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="15">
+    <row r="145" spans="1:2" ht="14.4">
       <c r="A145">
         <v>144</v>
       </c>
@@ -4868,7 +4871,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="15">
+    <row r="146" spans="1:2" ht="14.4">
       <c r="A146">
         <v>145</v>
       </c>
@@ -4876,7 +4879,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="15">
+    <row r="147" spans="1:2" ht="14.4">
       <c r="A147">
         <v>146</v>
       </c>
@@ -4884,7 +4887,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="15">
+    <row r="148" spans="1:2" ht="14.4">
       <c r="A148">
         <v>147</v>
       </c>
@@ -4892,7 +4895,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="15">
+    <row r="149" spans="1:2" ht="14.4">
       <c r="A149">
         <v>148</v>
       </c>
@@ -4900,7 +4903,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="15">
+    <row r="150" spans="1:2" ht="14.4">
       <c r="A150">
         <v>149</v>
       </c>
@@ -4908,7 +4911,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="15">
+    <row r="151" spans="1:2" ht="14.4">
       <c r="A151">
         <v>150</v>
       </c>
@@ -4916,7 +4919,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="152" spans="1:2" ht="15">
+    <row r="152" spans="1:2" ht="14.4">
       <c r="A152">
         <v>151</v>
       </c>
@@ -4924,7 +4927,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="153" spans="1:2" ht="15">
+    <row r="153" spans="1:2" ht="14.4">
       <c r="A153">
         <v>152</v>
       </c>
@@ -4932,7 +4935,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="154" spans="1:2" ht="15">
+    <row r="154" spans="1:2" ht="14.4">
       <c r="A154">
         <v>153</v>
       </c>
@@ -4940,7 +4943,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="155" spans="1:2" ht="15">
+    <row r="155" spans="1:2" ht="14.4">
       <c r="A155">
         <v>154</v>
       </c>
@@ -4948,7 +4951,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="156" spans="1:2" ht="15">
+    <row r="156" spans="1:2" ht="14.4">
       <c r="A156">
         <v>155</v>
       </c>
@@ -4956,7 +4959,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="157" spans="1:2" ht="15">
+    <row r="157" spans="1:2" ht="14.4">
       <c r="A157">
         <v>156</v>
       </c>
@@ -4964,7 +4967,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="15">
+    <row r="158" spans="1:2" ht="14.4">
       <c r="A158">
         <v>157</v>
       </c>
@@ -4972,7 +4975,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="159" spans="1:2" ht="15">
+    <row r="159" spans="1:2" ht="14.4">
       <c r="A159">
         <v>158</v>
       </c>
@@ -4980,7 +4983,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="160" spans="1:2" ht="15">
+    <row r="160" spans="1:2" ht="14.4">
       <c r="A160">
         <v>159</v>
       </c>
@@ -4988,7 +4991,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="161" spans="1:2" ht="15">
+    <row r="161" spans="1:2" ht="14.4">
       <c r="A161">
         <v>160</v>
       </c>
@@ -4996,7 +4999,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="15">
+    <row r="162" spans="1:2" ht="14.4">
       <c r="A162">
         <v>161</v>
       </c>
@@ -5004,7 +5007,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="15">
+    <row r="163" spans="1:2" ht="14.4">
       <c r="A163">
         <v>162</v>
       </c>
@@ -5012,7 +5015,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="15">
+    <row r="164" spans="1:2" ht="14.4">
       <c r="A164">
         <v>163</v>
       </c>
@@ -5020,7 +5023,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="15">
+    <row r="165" spans="1:2" ht="14.4">
       <c r="A165">
         <v>164</v>
       </c>
@@ -5028,7 +5031,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="166" spans="1:2" ht="15">
+    <row r="166" spans="1:2" ht="14.4">
       <c r="A166">
         <v>165</v>
       </c>
@@ -5044,7 +5047,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="168" spans="1:2" ht="15">
+    <row r="168" spans="1:2" ht="14.4">
       <c r="A168">
         <v>167</v>
       </c>
@@ -5052,7 +5055,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="169" spans="1:2" ht="15">
+    <row r="169" spans="1:2" ht="14.4">
       <c r="A169">
         <v>168</v>
       </c>
@@ -5060,7 +5063,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="170" spans="1:2" ht="15">
+    <row r="170" spans="1:2" ht="14.4">
       <c r="A170">
         <v>169</v>
       </c>
@@ -5068,7 +5071,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="171" spans="1:2" ht="15">
+    <row r="171" spans="1:2" ht="14.4">
       <c r="A171">
         <v>170</v>
       </c>
@@ -5076,7 +5079,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="172" spans="1:2" ht="15">
+    <row r="172" spans="1:2" ht="14.4">
       <c r="A172">
         <v>171</v>
       </c>
@@ -5084,7 +5087,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="173" spans="1:2" ht="15">
+    <row r="173" spans="1:2" ht="14.4">
       <c r="A173">
         <v>172</v>
       </c>
@@ -5092,7 +5095,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="174" spans="1:2" ht="15">
+    <row r="174" spans="1:2" ht="14.4">
       <c r="A174">
         <v>173</v>
       </c>
@@ -5100,7 +5103,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="175" spans="1:2" ht="15">
+    <row r="175" spans="1:2" ht="14.4">
       <c r="A175">
         <v>174</v>
       </c>
@@ -5108,7 +5111,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="176" spans="1:2" ht="15">
+    <row r="176" spans="1:2" ht="14.4">
       <c r="A176">
         <v>175</v>
       </c>
@@ -5116,7 +5119,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="177" spans="1:2" ht="15">
+    <row r="177" spans="1:2" ht="14.4">
       <c r="A177">
         <v>176</v>
       </c>
@@ -5124,7 +5127,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="178" spans="1:2" ht="15">
+    <row r="178" spans="1:2" ht="14.4">
       <c r="A178">
         <v>177</v>
       </c>
@@ -5132,7 +5135,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="179" spans="1:2" ht="15">
+    <row r="179" spans="1:2" ht="14.4">
       <c r="A179">
         <v>178</v>
       </c>
@@ -5140,7 +5143,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="180" spans="1:2" ht="15">
+    <row r="180" spans="1:2" ht="14.4">
       <c r="A180">
         <v>179</v>
       </c>
@@ -5302,20 +5305,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86060676-D353-469D-B400-DC39E59A0722}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:S180"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.25" customWidth="1"/>
-    <col min="4" max="4" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.125" customWidth="1"/>
-    <col min="6" max="6" width="31.25" style="59" customWidth="1"/>
-    <col min="14" max="14" width="41.125" customWidth="1"/>
-    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.19921875" customWidth="1"/>
+    <col min="4" max="4" width="23.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.09765625" customWidth="1"/>
+    <col min="6" max="6" width="31.19921875" style="59" customWidth="1"/>
+    <col min="14" max="14" width="41.09765625" customWidth="1"/>
+    <col min="15" max="15" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15">
+    <row r="1" spans="1:19" ht="14.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5351,11 +5354,11 @@
         <v>236</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15">
+    <row r="2" spans="1:19" ht="14.4">
       <c r="A2" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="97" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="4"/>
@@ -5371,7 +5374,7 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="98"/>
-      <c r="B3" s="104"/>
+      <c r="B3" s="97"/>
       <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
@@ -5402,7 +5405,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="98"/>
-      <c r="B4" s="104"/>
+      <c r="B4" s="97"/>
       <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
@@ -5433,7 +5436,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="98"/>
-      <c r="B5" s="104"/>
+      <c r="B5" s="97"/>
       <c r="C5" s="4" t="s">
         <v>12</v>
       </c>
@@ -5464,7 +5467,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="98"/>
-      <c r="B6" s="104"/>
+      <c r="B6" s="97"/>
       <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
@@ -5492,7 +5495,7 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="98"/>
-      <c r="B7" s="104"/>
+      <c r="B7" s="97"/>
       <c r="C7" s="4" t="s">
         <v>14</v>
       </c>
@@ -5520,7 +5523,7 @@
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="98"/>
-      <c r="B8" s="104"/>
+      <c r="B8" s="97"/>
       <c r="C8" s="4" t="s">
         <v>15</v>
       </c>
@@ -5543,7 +5546,7 @@
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="98"/>
-      <c r="B9" s="104"/>
+      <c r="B9" s="97"/>
       <c r="C9" s="4" t="s">
         <v>16</v>
       </c>
@@ -5564,7 +5567,7 @@
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="98"/>
-      <c r="B10" s="104"/>
+      <c r="B10" s="97"/>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
@@ -5579,7 +5582,7 @@
     </row>
     <row r="11" spans="1:19">
       <c r="A11" s="98"/>
-      <c r="B11" s="105" t="s">
+      <c r="B11" s="99" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="5"/>
@@ -5598,7 +5601,7 @@
     </row>
     <row r="12" spans="1:19">
       <c r="A12" s="98"/>
-      <c r="B12" s="105"/>
+      <c r="B12" s="99"/>
       <c r="C12" s="5" t="s">
         <v>60</v>
       </c>
@@ -5617,7 +5620,7 @@
     </row>
     <row r="13" spans="1:19">
       <c r="A13" s="98"/>
-      <c r="B13" s="105"/>
+      <c r="B13" s="99"/>
       <c r="C13" s="5" t="s">
         <v>61</v>
       </c>
@@ -5636,7 +5639,7 @@
     </row>
     <row r="14" spans="1:19">
       <c r="A14" s="98"/>
-      <c r="B14" s="105"/>
+      <c r="B14" s="99"/>
       <c r="C14" s="5" t="s">
         <v>62</v>
       </c>
@@ -5655,7 +5658,7 @@
     </row>
     <row r="15" spans="1:19">
       <c r="A15" s="98"/>
-      <c r="B15" s="105"/>
+      <c r="B15" s="99"/>
       <c r="C15" s="5" t="s">
         <v>63</v>
       </c>
@@ -5674,7 +5677,7 @@
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="98"/>
-      <c r="B16" s="105"/>
+      <c r="B16" s="99"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5" t="s">
         <v>67</v>
@@ -5691,7 +5694,7 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="98"/>
-      <c r="B17" s="105"/>
+      <c r="B17" s="99"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5" t="s">
         <v>68</v>
@@ -5708,7 +5711,7 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="98"/>
-      <c r="B18" s="104" t="s">
+      <c r="B18" s="97" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="4"/>
@@ -5727,7 +5730,7 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="98"/>
-      <c r="B19" s="104"/>
+      <c r="B19" s="97"/>
       <c r="C19" s="4" t="s">
         <v>7</v>
       </c>
@@ -5746,7 +5749,7 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="98"/>
-      <c r="B20" s="104"/>
+      <c r="B20" s="97"/>
       <c r="C20" s="4" t="s">
         <v>74</v>
       </c>
@@ -5765,7 +5768,7 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="98"/>
-      <c r="B21" s="104"/>
+      <c r="B21" s="97"/>
       <c r="C21" s="4" t="s">
         <v>75</v>
       </c>
@@ -5782,9 +5785,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15">
+    <row r="22" spans="1:17" ht="14.4">
       <c r="A22" s="98"/>
-      <c r="B22" s="104"/>
+      <c r="B22" s="97"/>
       <c r="C22" s="4" t="s">
         <v>76</v>
       </c>
@@ -5800,9 +5803,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15">
+    <row r="23" spans="1:17" ht="14.4">
       <c r="A23" s="98"/>
-      <c r="B23" s="104"/>
+      <c r="B23" s="97"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4" t="s">
         <v>67</v>
@@ -5816,9 +5819,9 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15">
+    <row r="24" spans="1:17" ht="14.4">
       <c r="A24" s="98"/>
-      <c r="B24" s="105" t="s">
+      <c r="B24" s="99" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6"/>
@@ -5832,9 +5835,9 @@
         <v>615</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75">
+    <row r="25" spans="1:17" ht="15.6">
       <c r="A25" s="98"/>
-      <c r="B25" s="105"/>
+      <c r="B25" s="99"/>
       <c r="C25" s="6" t="s">
         <v>81</v>
       </c>
@@ -5848,9 +5851,9 @@
         <v>730</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15">
+    <row r="26" spans="1:17" ht="14.4">
       <c r="A26" s="98"/>
-      <c r="B26" s="105"/>
+      <c r="B26" s="99"/>
       <c r="C26" s="6" t="s">
         <v>82</v>
       </c>
@@ -5865,9 +5868,9 @@
         <v>731</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15">
+    <row r="27" spans="1:17" ht="14.4">
       <c r="A27" s="98"/>
-      <c r="B27" s="105"/>
+      <c r="B27" s="99"/>
       <c r="C27" s="5"/>
       <c r="D27" s="6" t="s">
         <v>84</v>
@@ -5880,9 +5883,9 @@
         <v>732</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="15">
+    <row r="28" spans="1:17" ht="14.4">
       <c r="A28" s="98"/>
-      <c r="B28" s="105"/>
+      <c r="B28" s="99"/>
       <c r="C28" s="5"/>
       <c r="D28" s="6" t="s">
         <v>78</v>
@@ -5894,7 +5897,7 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="98"/>
-      <c r="B29" s="106" t="s">
+      <c r="B29" s="100" t="s">
         <v>85</v>
       </c>
       <c r="C29" s="4"/>
@@ -5908,9 +5911,9 @@
         <v>734</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75">
+    <row r="30" spans="1:17" ht="15.6">
       <c r="A30" s="98"/>
-      <c r="B30" s="106"/>
+      <c r="B30" s="100"/>
       <c r="C30" s="4" t="s">
         <v>86</v>
       </c>
@@ -5925,9 +5928,9 @@
         <v>735</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75">
+    <row r="31" spans="1:17" ht="15.6">
       <c r="A31" s="98"/>
-      <c r="B31" s="106"/>
+      <c r="B31" s="100"/>
       <c r="C31" s="4" t="s">
         <v>87</v>
       </c>
@@ -5942,9 +5945,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15">
+    <row r="32" spans="1:17" ht="14.4">
       <c r="A32" s="98"/>
-      <c r="B32" s="106"/>
+      <c r="B32" s="100"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="7" t="s">
@@ -5954,9 +5957,9 @@
         <v>737</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15">
+    <row r="33" spans="1:16" ht="14.4">
       <c r="A33" s="98"/>
-      <c r="B33" s="107" t="s">
+      <c r="B33" s="101" t="s">
         <v>93</v>
       </c>
       <c r="C33" s="6"/>
@@ -5973,7 +5976,7 @@
     </row>
     <row r="34" spans="1:16" ht="15" customHeight="1">
       <c r="A34" s="98"/>
-      <c r="B34" s="107"/>
+      <c r="B34" s="101"/>
       <c r="C34" s="6" t="s">
         <v>94</v>
       </c>
@@ -5988,9 +5991,9 @@
         <v>739</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15">
+    <row r="35" spans="1:16" ht="14.4">
       <c r="A35" s="98"/>
-      <c r="B35" s="107"/>
+      <c r="B35" s="101"/>
       <c r="C35" s="6" t="s">
         <v>95</v>
       </c>
@@ -6005,9 +6008,9 @@
         <v>740</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="15">
+    <row r="36" spans="1:16" ht="14.4">
       <c r="A36" s="98"/>
-      <c r="B36" s="100" t="s">
+      <c r="B36" s="102" t="s">
         <v>211</v>
       </c>
       <c r="C36" s="7"/>
@@ -6022,9 +6025,9 @@
         <v>741</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="15">
+    <row r="37" spans="1:16" ht="14.4">
       <c r="A37" s="98"/>
-      <c r="B37" s="100"/>
+      <c r="B37" s="102"/>
       <c r="C37" s="7" t="s">
         <v>97</v>
       </c>
@@ -6039,9 +6042,9 @@
         <v>736</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="15">
+    <row r="38" spans="1:16" ht="14.4">
       <c r="A38" s="98"/>
-      <c r="B38" s="100"/>
+      <c r="B38" s="102"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7" t="s">
         <v>64</v>
@@ -6054,9 +6057,9 @@
         <v>742</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="15">
+    <row r="39" spans="1:16" ht="14.4">
       <c r="A39" s="98"/>
-      <c r="B39" s="100"/>
+      <c r="B39" s="102"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7" t="s">
@@ -6067,9 +6070,9 @@
         <v>743</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="15">
+    <row r="40" spans="1:16" ht="14.4">
       <c r="A40" s="98"/>
-      <c r="B40" s="102" t="s">
+      <c r="B40" s="103" t="s">
         <v>212</v>
       </c>
       <c r="C40" s="6"/>
@@ -6084,9 +6087,9 @@
         <v>744</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="15">
+    <row r="41" spans="1:16" ht="14.4">
       <c r="A41" s="98"/>
-      <c r="B41" s="102"/>
+      <c r="B41" s="103"/>
       <c r="C41" s="6" t="s">
         <v>214</v>
       </c>
@@ -6100,9 +6103,9 @@
         <v>745</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="15">
+    <row r="42" spans="1:16" ht="14.4">
       <c r="A42" s="98"/>
-      <c r="B42" s="102"/>
+      <c r="B42" s="103"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6" t="s">
         <v>66</v>
@@ -6115,9 +6118,9 @@
         <v>746</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="15">
+    <row r="43" spans="1:16" ht="14.4">
       <c r="A43" s="98"/>
-      <c r="B43" s="102"/>
+      <c r="B43" s="103"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="s">
@@ -6128,9 +6131,9 @@
         <v>747</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="15">
+    <row r="44" spans="1:16" ht="14.4">
       <c r="A44" s="98"/>
-      <c r="B44" s="100" t="s">
+      <c r="B44" s="102" t="s">
         <v>213</v>
       </c>
       <c r="C44" s="7"/>
@@ -6145,9 +6148,9 @@
         <v>748</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="15">
+    <row r="45" spans="1:16" ht="14.4">
       <c r="A45" s="98"/>
-      <c r="B45" s="100"/>
+      <c r="B45" s="102"/>
       <c r="C45" s="7" t="s">
         <v>101</v>
       </c>
@@ -6162,9 +6165,9 @@
         <v>749</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="15">
+    <row r="46" spans="1:16" ht="14.4">
       <c r="A46" s="98"/>
-      <c r="B46" s="100"/>
+      <c r="B46" s="102"/>
       <c r="C46" s="7" t="s">
         <v>102</v>
       </c>
@@ -6179,9 +6182,9 @@
         <v>750</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="15">
+    <row r="47" spans="1:16" ht="14.4">
       <c r="A47" s="98"/>
-      <c r="B47" s="100"/>
+      <c r="B47" s="102"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7" t="s">
@@ -6192,17 +6195,17 @@
         <v>751</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="15">
+    <row r="48" spans="1:16" ht="14.4">
       <c r="F48" s="60"/>
       <c r="P48" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="15">
-      <c r="A49" s="103" t="s">
+    <row r="49" spans="1:16" ht="14.4">
+      <c r="A49" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="B49" s="100" t="s">
+      <c r="B49" s="102" t="s">
         <v>104</v>
       </c>
       <c r="C49" s="7"/>
@@ -6217,9 +6220,9 @@
         <v>753</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="15">
-      <c r="A50" s="103"/>
-      <c r="B50" s="100"/>
+    <row r="50" spans="1:16" ht="14.4">
+      <c r="A50" s="105"/>
+      <c r="B50" s="102"/>
       <c r="C50" s="7" t="s">
         <v>105</v>
       </c>
@@ -6234,9 +6237,9 @@
         <v>754</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="15">
-      <c r="A51" s="103"/>
-      <c r="B51" s="100"/>
+    <row r="51" spans="1:16" ht="14.4">
+      <c r="A51" s="105"/>
+      <c r="B51" s="102"/>
       <c r="C51" s="7" t="s">
         <v>107</v>
       </c>
@@ -6251,9 +6254,9 @@
         <v>755</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="15">
-      <c r="A52" s="103"/>
-      <c r="B52" s="100"/>
+    <row r="52" spans="1:16" ht="14.4">
+      <c r="A52" s="105"/>
+      <c r="B52" s="102"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7" t="s">
         <v>109</v>
@@ -6266,9 +6269,9 @@
         <v>756</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="15">
-      <c r="A53" s="103"/>
-      <c r="B53" s="100"/>
+    <row r="53" spans="1:16" ht="14.4">
+      <c r="A53" s="105"/>
+      <c r="B53" s="102"/>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7">
@@ -6279,8 +6282,8 @@
         <v>757</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="15">
-      <c r="A54" s="103"/>
+    <row r="54" spans="1:16" ht="14.4">
+      <c r="A54" s="105"/>
       <c r="B54" s="8"/>
       <c r="C54" s="7" t="s">
         <v>215</v>
@@ -6296,9 +6299,9 @@
         <v>758</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="15">
-      <c r="A55" s="103"/>
-      <c r="B55" s="99" t="s">
+    <row r="55" spans="1:16" ht="14.4">
+      <c r="A55" s="105"/>
+      <c r="B55" s="104" t="s">
         <v>110</v>
       </c>
       <c r="C55" s="6" t="s">
@@ -6315,9 +6318,9 @@
         <v>759</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="15">
-      <c r="A56" s="103"/>
-      <c r="B56" s="99"/>
+    <row r="56" spans="1:16" ht="14.4">
+      <c r="A56" s="105"/>
+      <c r="B56" s="104"/>
       <c r="C56" s="6" t="s">
         <v>112</v>
       </c>
@@ -6332,9 +6335,9 @@
         <v>760</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="15">
-      <c r="A57" s="103"/>
-      <c r="B57" s="99"/>
+    <row r="57" spans="1:16" ht="14.4">
+      <c r="A57" s="105"/>
+      <c r="B57" s="104"/>
       <c r="C57" s="6"/>
       <c r="D57" s="6"/>
       <c r="E57" s="6" t="s">
@@ -6345,9 +6348,9 @@
         <v>761</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="15">
-      <c r="A58" s="103"/>
-      <c r="B58" s="99"/>
+    <row r="58" spans="1:16" ht="14.4">
+      <c r="A58" s="105"/>
+      <c r="B58" s="104"/>
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
       <c r="E58" s="6" t="s">
@@ -6358,8 +6361,8 @@
         <v>762</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="15">
-      <c r="A59" s="103"/>
+    <row r="59" spans="1:16" ht="14.4">
+      <c r="A59" s="105"/>
       <c r="B59" s="57"/>
       <c r="C59" s="6"/>
       <c r="D59" s="6"/>
@@ -6371,9 +6374,9 @@
         <v>763</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="15">
-      <c r="A60" s="103"/>
-      <c r="B60" s="100" t="s">
+    <row r="60" spans="1:16" ht="14.4">
+      <c r="A60" s="105"/>
+      <c r="B60" s="102" t="s">
         <v>116</v>
       </c>
       <c r="C60" s="7" t="s">
@@ -6390,9 +6393,9 @@
         <v>764</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="15">
-      <c r="A61" s="103"/>
-      <c r="B61" s="100"/>
+    <row r="61" spans="1:16" ht="14.4">
+      <c r="A61" s="105"/>
+      <c r="B61" s="102"/>
       <c r="C61" s="7" t="s">
         <v>116</v>
       </c>
@@ -6407,9 +6410,9 @@
         <v>765</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="16.899999999999999" customHeight="1">
-      <c r="A62" s="103"/>
-      <c r="B62" s="100"/>
+    <row r="62" spans="1:16" ht="16.95" customHeight="1">
+      <c r="A62" s="105"/>
+      <c r="B62" s="102"/>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7" t="s">
@@ -6420,8 +6423,8 @@
         <v>766</v>
       </c>
     </row>
-    <row r="63" spans="1:16" ht="16.899999999999999" customHeight="1">
-      <c r="A63" s="103"/>
+    <row r="63" spans="1:16" ht="16.95" customHeight="1">
+      <c r="A63" s="105"/>
       <c r="B63" s="8"/>
       <c r="C63" s="61"/>
       <c r="D63" s="6"/>
@@ -6433,9 +6436,9 @@
         <v>767</v>
       </c>
     </row>
-    <row r="64" spans="1:16" ht="15">
-      <c r="A64" s="103"/>
-      <c r="B64" s="99" t="s">
+    <row r="64" spans="1:16" ht="14.4">
+      <c r="A64" s="105"/>
+      <c r="B64" s="104" t="s">
         <v>121</v>
       </c>
       <c r="C64" s="6"/>
@@ -6450,9 +6453,9 @@
         <v>734</v>
       </c>
     </row>
-    <row r="65" spans="1:16" ht="15">
-      <c r="A65" s="103"/>
-      <c r="B65" s="99"/>
+    <row r="65" spans="1:16" ht="14.4">
+      <c r="A65" s="105"/>
+      <c r="B65" s="104"/>
       <c r="C65" s="6" t="s">
         <v>121</v>
       </c>
@@ -6467,9 +6470,9 @@
         <v>768</v>
       </c>
     </row>
-    <row r="66" spans="1:16" ht="15">
-      <c r="A66" s="103"/>
-      <c r="B66" s="99"/>
+    <row r="66" spans="1:16" ht="14.4">
+      <c r="A66" s="105"/>
+      <c r="B66" s="104"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6" t="s">
@@ -6480,8 +6483,8 @@
         <v>769</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="15">
-      <c r="A67" s="103"/>
+    <row r="67" spans="1:16" ht="14.4">
+      <c r="A67" s="105"/>
       <c r="B67" s="10" t="s">
         <v>242</v>
       </c>
@@ -6499,9 +6502,9 @@
         <v>770</v>
       </c>
     </row>
-    <row r="68" spans="1:16" ht="15">
-      <c r="A68" s="103"/>
-      <c r="B68" s="99" t="s">
+    <row r="68" spans="1:16" ht="14.4">
+      <c r="A68" s="105"/>
+      <c r="B68" s="104" t="s">
         <v>243</v>
       </c>
       <c r="C68" s="6"/>
@@ -6516,9 +6519,9 @@
         <v>771</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="15">
-      <c r="A69" s="103"/>
-      <c r="B69" s="99"/>
+    <row r="69" spans="1:16" ht="14.4">
+      <c r="A69" s="105"/>
+      <c r="B69" s="104"/>
       <c r="C69" s="6" t="s">
         <v>126</v>
       </c>
@@ -6533,9 +6536,9 @@
         <v>772</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="15">
-      <c r="A70" s="103"/>
-      <c r="B70" s="99"/>
+    <row r="70" spans="1:16" ht="14.4">
+      <c r="A70" s="105"/>
+      <c r="B70" s="104"/>
       <c r="C70" s="6" t="s">
         <v>128</v>
       </c>
@@ -6548,9 +6551,9 @@
         <v>773</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="15">
-      <c r="A71" s="103"/>
-      <c r="B71" s="99"/>
+    <row r="71" spans="1:16" ht="14.4">
+      <c r="A71" s="105"/>
+      <c r="B71" s="104"/>
       <c r="C71" s="6" t="s">
         <v>130</v>
       </c>
@@ -6563,9 +6566,9 @@
         <v>774</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="15">
-      <c r="A72" s="103"/>
-      <c r="B72" s="99"/>
+    <row r="72" spans="1:16" ht="14.4">
+      <c r="A72" s="105"/>
+      <c r="B72" s="104"/>
       <c r="C72" s="6"/>
       <c r="D72" s="6"/>
       <c r="E72" s="6" t="s">
@@ -6576,9 +6579,9 @@
         <v>775</v>
       </c>
     </row>
-    <row r="73" spans="1:16" ht="15">
-      <c r="A73" s="103"/>
-      <c r="B73" s="99"/>
+    <row r="73" spans="1:16" ht="14.4">
+      <c r="A73" s="105"/>
+      <c r="B73" s="104"/>
       <c r="C73" s="61"/>
       <c r="D73" s="6"/>
       <c r="E73" s="6" t="s">
@@ -6589,9 +6592,9 @@
         <v>776</v>
       </c>
     </row>
-    <row r="74" spans="1:16" ht="15">
-      <c r="A74" s="103"/>
-      <c r="B74" s="100" t="s">
+    <row r="74" spans="1:16" ht="14.4">
+      <c r="A74" s="105"/>
+      <c r="B74" s="102" t="s">
         <v>134</v>
       </c>
       <c r="C74" s="7"/>
@@ -6606,9 +6609,9 @@
         <v>777</v>
       </c>
     </row>
-    <row r="75" spans="1:16" ht="15">
-      <c r="A75" s="103"/>
-      <c r="B75" s="100"/>
+    <row r="75" spans="1:16" ht="14.4">
+      <c r="A75" s="105"/>
+      <c r="B75" s="102"/>
       <c r="C75" s="7" t="s">
         <v>135</v>
       </c>
@@ -6623,9 +6626,9 @@
         <v>778</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="15">
-      <c r="A76" s="103"/>
-      <c r="B76" s="100"/>
+    <row r="76" spans="1:16" ht="14.4">
+      <c r="A76" s="105"/>
+      <c r="B76" s="102"/>
       <c r="C76" s="7" t="s">
         <v>136</v>
       </c>
@@ -6638,9 +6641,9 @@
         <v>779</v>
       </c>
     </row>
-    <row r="77" spans="1:16" ht="15">
-      <c r="A77" s="103"/>
-      <c r="B77" s="100"/>
+    <row r="77" spans="1:16" ht="14.4">
+      <c r="A77" s="105"/>
+      <c r="B77" s="102"/>
       <c r="C77" s="7" t="s">
         <v>137</v>
       </c>
@@ -6650,9 +6653,9 @@
         <v>768</v>
       </c>
     </row>
-    <row r="78" spans="1:16" ht="15">
-      <c r="A78" s="103"/>
-      <c r="B78" s="100"/>
+    <row r="78" spans="1:16" ht="14.4">
+      <c r="A78" s="105"/>
+      <c r="B78" s="102"/>
       <c r="C78" s="7" t="s">
         <v>138</v>
       </c>
@@ -6662,9 +6665,9 @@
         <v>780</v>
       </c>
     </row>
-    <row r="79" spans="1:16" ht="15">
-      <c r="A79" s="103"/>
-      <c r="B79" s="100"/>
+    <row r="79" spans="1:16" ht="14.4">
+      <c r="A79" s="105"/>
+      <c r="B79" s="102"/>
       <c r="C79" s="7" t="s">
         <v>139</v>
       </c>
@@ -6674,17 +6677,17 @@
         <v>781</v>
       </c>
     </row>
-    <row r="80" spans="1:16" ht="15">
-      <c r="A80" s="103"/>
-      <c r="B80" s="100"/>
+    <row r="80" spans="1:16" ht="14.4">
+      <c r="A80" s="105"/>
+      <c r="B80" s="102"/>
       <c r="C80" s="7" t="s">
         <v>140</v>
       </c>
       <c r="D80" s="7"/>
       <c r="E80" s="7"/>
     </row>
-    <row r="81" spans="1:14" ht="15">
-      <c r="A81" s="103"/>
+    <row r="81" spans="1:14" ht="14.4">
+      <c r="A81" s="105"/>
       <c r="B81" s="8"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7" t="s">
@@ -6694,9 +6697,9 @@
         <v>215</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="15">
-      <c r="A82" s="103"/>
-      <c r="B82" s="99" t="s">
+    <row r="82" spans="1:14" ht="14.4">
+      <c r="A82" s="105"/>
+      <c r="B82" s="104" t="s">
         <v>141</v>
       </c>
       <c r="C82" s="6" t="s">
@@ -6709,9 +6712,9 @@
         <v>143</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="15">
-      <c r="A83" s="103"/>
-      <c r="B83" s="99"/>
+    <row r="83" spans="1:14" ht="14.4">
+      <c r="A83" s="105"/>
+      <c r="B83" s="104"/>
       <c r="C83" s="6" t="s">
         <v>144</v>
       </c>
@@ -6720,9 +6723,9 @@
         <v>145</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="15">
-      <c r="A84" s="103"/>
-      <c r="B84" s="99"/>
+    <row r="84" spans="1:14" ht="14.4">
+      <c r="A84" s="105"/>
+      <c r="B84" s="104"/>
       <c r="C84" s="6" t="s">
         <v>146</v>
       </c>
@@ -6731,18 +6734,18 @@
         <v>147</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A85" s="103"/>
-      <c r="B85" s="99"/>
+    <row r="85" spans="1:14" ht="15" thickBot="1">
+      <c r="A85" s="105"/>
+      <c r="B85" s="104"/>
       <c r="C85" s="6"/>
       <c r="D85" s="6"/>
       <c r="E85" s="6" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A86" s="103"/>
-      <c r="B86" s="99"/>
+    <row r="86" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A86" s="105"/>
+      <c r="B86" s="104"/>
       <c r="C86" s="6"/>
       <c r="D86" s="6"/>
       <c r="E86" s="6" t="s">
@@ -6750,9 +6753,9 @@
       </c>
       <c r="N86" s="23"/>
     </row>
-    <row r="87" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A87" s="103"/>
-      <c r="B87" s="100" t="s">
+    <row r="87" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A87" s="105"/>
+      <c r="B87" s="102" t="s">
         <v>150</v>
       </c>
       <c r="C87" s="7"/>
@@ -6764,9 +6767,9 @@
       </c>
       <c r="N87" s="23"/>
     </row>
-    <row r="88" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A88" s="103"/>
-      <c r="B88" s="100"/>
+    <row r="88" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A88" s="105"/>
+      <c r="B88" s="102"/>
       <c r="C88" s="7" t="s">
         <v>151</v>
       </c>
@@ -6778,9 +6781,9 @@
       </c>
       <c r="N88" s="23"/>
     </row>
-    <row r="89" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A89" s="103"/>
-      <c r="B89" s="100"/>
+    <row r="89" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A89" s="105"/>
+      <c r="B89" s="102"/>
       <c r="C89" s="7" t="s">
         <v>153</v>
       </c>
@@ -6790,9 +6793,9 @@
       </c>
       <c r="N89" s="23"/>
     </row>
-    <row r="90" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A90" s="103"/>
-      <c r="B90" s="100"/>
+    <row r="90" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A90" s="105"/>
+      <c r="B90" s="102"/>
       <c r="C90" s="7" t="s">
         <v>155</v>
       </c>
@@ -6802,9 +6805,9 @@
       </c>
       <c r="N90" s="23"/>
     </row>
-    <row r="91" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A91" s="103"/>
-      <c r="B91" s="100"/>
+    <row r="91" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A91" s="105"/>
+      <c r="B91" s="102"/>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
       <c r="E91" s="7" t="s">
@@ -6812,8 +6815,8 @@
       </c>
       <c r="N91" s="23"/>
     </row>
-    <row r="92" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A92" s="103"/>
+    <row r="92" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A92" s="105"/>
       <c r="B92" s="11" t="s">
         <v>158</v>
       </c>
@@ -6828,9 +6831,9 @@
       </c>
       <c r="N92" s="23"/>
     </row>
-    <row r="93" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A93" s="103"/>
-      <c r="B93" s="100" t="s">
+    <row r="93" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A93" s="105"/>
+      <c r="B93" s="102" t="s">
         <v>244</v>
       </c>
       <c r="C93" s="7"/>
@@ -6840,9 +6843,9 @@
       </c>
       <c r="N93" s="23"/>
     </row>
-    <row r="94" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A94" s="103"/>
-      <c r="B94" s="100"/>
+    <row r="94" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A94" s="105"/>
+      <c r="B94" s="102"/>
       <c r="C94" s="7"/>
       <c r="D94" s="7" t="s">
         <v>215</v>
@@ -6852,9 +6855,9 @@
       </c>
       <c r="N94" s="23"/>
     </row>
-    <row r="95" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A95" s="103"/>
-      <c r="B95" s="100"/>
+    <row r="95" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A95" s="105"/>
+      <c r="B95" s="102"/>
       <c r="C95" s="7" t="s">
         <v>244</v>
       </c>
@@ -6864,9 +6867,9 @@
       </c>
       <c r="N95" s="23"/>
     </row>
-    <row r="96" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A96" s="103"/>
-      <c r="B96" s="99" t="s">
+    <row r="96" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A96" s="105"/>
+      <c r="B96" s="104" t="s">
         <v>249</v>
       </c>
       <c r="C96" s="6"/>
@@ -6878,9 +6881,9 @@
       </c>
       <c r="N96" s="23"/>
     </row>
-    <row r="97" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A97" s="103"/>
-      <c r="B97" s="99"/>
+    <row r="97" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A97" s="105"/>
+      <c r="B97" s="104"/>
       <c r="C97" s="6"/>
       <c r="D97" s="6"/>
       <c r="E97" s="6" t="s">
@@ -6888,9 +6891,9 @@
       </c>
       <c r="N97" s="23"/>
     </row>
-    <row r="98" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A98" s="103"/>
-      <c r="B98" s="99"/>
+    <row r="98" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A98" s="105"/>
+      <c r="B98" s="104"/>
       <c r="C98" s="6" t="s">
         <v>249</v>
       </c>
@@ -6900,9 +6903,9 @@
       </c>
       <c r="N98" s="23"/>
     </row>
-    <row r="99" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A99" s="103"/>
-      <c r="B99" s="99"/>
+    <row r="99" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A99" s="105"/>
+      <c r="B99" s="104"/>
       <c r="C99" s="6"/>
       <c r="D99" s="6"/>
       <c r="E99" s="6" t="s">
@@ -6910,8 +6913,8 @@
       </c>
       <c r="N99" s="24"/>
     </row>
-    <row r="100" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A100" s="103"/>
+    <row r="100" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A100" s="105"/>
       <c r="B100" s="57"/>
       <c r="C100" s="6"/>
       <c r="D100" s="6"/>
@@ -6920,9 +6923,9 @@
       </c>
       <c r="N100" s="24"/>
     </row>
-    <row r="101" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A101" s="103"/>
-      <c r="B101" s="100" t="s">
+    <row r="101" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A101" s="105"/>
+      <c r="B101" s="102" t="s">
         <v>162</v>
       </c>
       <c r="C101" s="7" t="s">
@@ -6936,9 +6939,9 @@
       </c>
       <c r="N101" s="24"/>
     </row>
-    <row r="102" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A102" s="103"/>
-      <c r="B102" s="100"/>
+    <row r="102" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A102" s="105"/>
+      <c r="B102" s="102"/>
       <c r="C102" s="7"/>
       <c r="D102" s="7"/>
       <c r="E102" s="7" t="s">
@@ -6946,8 +6949,8 @@
       </c>
       <c r="N102" s="24"/>
     </row>
-    <row r="103" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A103" s="103"/>
+    <row r="103" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A103" s="105"/>
       <c r="B103" s="8"/>
       <c r="C103" s="7"/>
       <c r="D103" s="7" t="s">
@@ -6958,9 +6961,9 @@
       </c>
       <c r="N103" s="62"/>
     </row>
-    <row r="104" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A104" s="103"/>
-      <c r="B104" s="99" t="s">
+    <row r="104" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A104" s="105"/>
+      <c r="B104" s="104" t="s">
         <v>164</v>
       </c>
       <c r="C104" s="6" t="s">
@@ -6972,9 +6975,9 @@
       </c>
       <c r="N104" s="22"/>
     </row>
-    <row r="105" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A105" s="103"/>
-      <c r="B105" s="99"/>
+    <row r="105" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A105" s="105"/>
+      <c r="B105" s="104"/>
       <c r="C105" s="6" t="s">
         <v>164</v>
       </c>
@@ -6984,9 +6987,9 @@
       </c>
       <c r="N105" s="23"/>
     </row>
-    <row r="106" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A106" s="103"/>
-      <c r="B106" s="99"/>
+    <row r="106" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A106" s="105"/>
+      <c r="B106" s="104"/>
       <c r="C106" s="6"/>
       <c r="D106" s="6"/>
       <c r="E106" s="6" t="s">
@@ -6994,9 +6997,9 @@
       </c>
       <c r="N106" s="23"/>
     </row>
-    <row r="107" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A107" s="103"/>
-      <c r="B107" s="99"/>
+    <row r="107" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A107" s="105"/>
+      <c r="B107" s="104"/>
       <c r="C107" s="6"/>
       <c r="D107" s="6"/>
       <c r="E107" s="6" t="s">
@@ -7004,9 +7007,9 @@
       </c>
       <c r="N107" s="23"/>
     </row>
-    <row r="108" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A108" s="103"/>
-      <c r="B108" s="99"/>
+    <row r="108" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A108" s="105"/>
+      <c r="B108" s="104"/>
       <c r="C108" s="6"/>
       <c r="D108" s="6"/>
       <c r="E108" s="6" t="s">
@@ -7014,9 +7017,9 @@
       </c>
       <c r="N108" s="23"/>
     </row>
-    <row r="109" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A109" s="103"/>
-      <c r="B109" s="100" t="s">
+    <row r="109" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A109" s="105"/>
+      <c r="B109" s="102" t="s">
         <v>245</v>
       </c>
       <c r="C109" s="7" t="s">
@@ -7030,9 +7033,9 @@
       </c>
       <c r="N109" s="23"/>
     </row>
-    <row r="110" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A110" s="103"/>
-      <c r="B110" s="100"/>
+    <row r="110" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A110" s="105"/>
+      <c r="B110" s="102"/>
       <c r="C110" s="7" t="s">
         <v>172</v>
       </c>
@@ -7040,9 +7043,9 @@
       <c r="E110" s="7"/>
       <c r="N110" s="25"/>
     </row>
-    <row r="111" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A111" s="103"/>
-      <c r="B111" s="99" t="s">
+    <row r="111" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A111" s="105"/>
+      <c r="B111" s="104" t="s">
         <v>173</v>
       </c>
       <c r="C111" s="6"/>
@@ -7052,9 +7055,9 @@
       </c>
       <c r="N111" s="25"/>
     </row>
-    <row r="112" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A112" s="103"/>
-      <c r="B112" s="99"/>
+    <row r="112" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A112" s="105"/>
+      <c r="B112" s="104"/>
       <c r="C112" s="6"/>
       <c r="D112" s="6" t="s">
         <v>215</v>
@@ -7064,9 +7067,9 @@
       </c>
       <c r="N112" s="25"/>
     </row>
-    <row r="113" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A113" s="103"/>
-      <c r="B113" s="99"/>
+    <row r="113" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A113" s="105"/>
+      <c r="B113" s="104"/>
       <c r="C113" s="6" t="s">
         <v>173</v>
       </c>
@@ -7076,8 +7079,8 @@
       </c>
       <c r="N113" s="26"/>
     </row>
-    <row r="114" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A114" s="103"/>
+    <row r="114" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A114" s="105"/>
       <c r="B114" s="13" t="s">
         <v>246</v>
       </c>
@@ -7092,8 +7095,8 @@
       </c>
       <c r="N114" s="26"/>
     </row>
-    <row r="115" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A115" s="103"/>
+    <row r="115" spans="1:14" ht="15" thickBot="1">
+      <c r="A115" s="105"/>
       <c r="B115" s="12" t="s">
         <v>174</v>
       </c>
@@ -7108,8 +7111,8 @@
       </c>
       <c r="N115" s="20"/>
     </row>
-    <row r="116" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A116" s="103"/>
+    <row r="116" spans="1:14" ht="15" thickBot="1">
+      <c r="A116" s="105"/>
       <c r="B116" s="13" t="s">
         <v>247</v>
       </c>
@@ -7124,8 +7127,8 @@
       </c>
       <c r="N116" s="21"/>
     </row>
-    <row r="117" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A117" s="103"/>
+    <row r="117" spans="1:14" ht="15" thickBot="1">
+      <c r="A117" s="105"/>
       <c r="B117" s="12" t="s">
         <v>175</v>
       </c>
@@ -7140,8 +7143,8 @@
       </c>
       <c r="N117" s="21"/>
     </row>
-    <row r="118" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A118" s="103"/>
+    <row r="118" spans="1:14" ht="15" thickBot="1">
+      <c r="A118" s="105"/>
       <c r="B118" s="17" t="s">
         <v>248</v>
       </c>
@@ -7156,10 +7159,10 @@
       </c>
       <c r="N118" s="21"/>
     </row>
-    <row r="119" spans="1:14" ht="15.75" thickBot="1">
+    <row r="119" spans="1:14" ht="15" thickBot="1">
       <c r="N119" s="21"/>
     </row>
-    <row r="120" spans="1:14" ht="15.75" thickBot="1">
+    <row r="120" spans="1:14" ht="15" thickBot="1">
       <c r="D120" t="s">
         <v>215</v>
       </c>
@@ -7168,11 +7171,11 @@
       </c>
       <c r="N120" s="21"/>
     </row>
-    <row r="121" spans="1:14" ht="15.75" thickBot="1">
+    <row r="121" spans="1:14" ht="15" thickBot="1">
       <c r="A121" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="B121" s="99" t="s">
+      <c r="B121" s="104" t="s">
         <v>252</v>
       </c>
       <c r="C121" s="6"/>
@@ -7184,9 +7187,9 @@
       </c>
       <c r="N121" s="21"/>
     </row>
-    <row r="122" spans="1:14" ht="15.75" thickBot="1">
+    <row r="122" spans="1:14" ht="15" thickBot="1">
       <c r="A122" s="98"/>
-      <c r="B122" s="99"/>
+      <c r="B122" s="104"/>
       <c r="C122" s="6"/>
       <c r="D122" s="6" t="s">
         <v>78</v>
@@ -7196,7 +7199,7 @@
       </c>
       <c r="N122" s="21"/>
     </row>
-    <row r="123" spans="1:14" ht="15.75" thickBot="1">
+    <row r="123" spans="1:14" ht="15" thickBot="1">
       <c r="A123" s="98"/>
       <c r="B123" s="57"/>
       <c r="C123" s="6"/>
@@ -7208,9 +7211,9 @@
       </c>
       <c r="N123" s="21"/>
     </row>
-    <row r="124" spans="1:14" ht="15.75" thickBot="1">
+    <row r="124" spans="1:14" ht="15" thickBot="1">
       <c r="A124" s="98"/>
-      <c r="B124" s="100" t="s">
+      <c r="B124" s="102" t="s">
         <v>176</v>
       </c>
       <c r="C124" s="7"/>
@@ -7222,9 +7225,9 @@
       </c>
       <c r="N124" s="21"/>
     </row>
-    <row r="125" spans="1:14" ht="15.75" thickBot="1">
+    <row r="125" spans="1:14" ht="15" thickBot="1">
       <c r="A125" s="98"/>
-      <c r="B125" s="100"/>
+      <c r="B125" s="102"/>
       <c r="C125" s="7" t="s">
         <v>176</v>
       </c>
@@ -7234,9 +7237,9 @@
       <c r="E125" s="7"/>
       <c r="N125" s="21"/>
     </row>
-    <row r="126" spans="1:14" ht="15.75" thickBot="1">
+    <row r="126" spans="1:14" ht="15" thickBot="1">
       <c r="A126" s="98"/>
-      <c r="B126" s="99" t="s">
+      <c r="B126" s="104" t="s">
         <v>250</v>
       </c>
       <c r="C126" s="6" t="s">
@@ -7250,9 +7253,9 @@
       </c>
       <c r="N126" s="21"/>
     </row>
-    <row r="127" spans="1:14" ht="15.75" thickBot="1">
+    <row r="127" spans="1:14" ht="15" thickBot="1">
       <c r="A127" s="98"/>
-      <c r="B127" s="99"/>
+      <c r="B127" s="104"/>
       <c r="C127" s="6"/>
       <c r="D127" s="6" t="s">
         <v>215</v>
@@ -7262,7 +7265,7 @@
       </c>
       <c r="N127" s="21"/>
     </row>
-    <row r="128" spans="1:14" ht="15.75" thickBot="1">
+    <row r="128" spans="1:14" ht="15" thickBot="1">
       <c r="A128" s="98"/>
       <c r="B128" s="8" t="s">
         <v>251</v>
@@ -7278,7 +7281,7 @@
       </c>
       <c r="N128" s="21"/>
     </row>
-    <row r="129" spans="1:14" ht="16.5" thickBot="1">
+    <row r="129" spans="1:14" ht="16.2" thickBot="1">
       <c r="A129" s="98"/>
       <c r="B129" s="12" t="s">
         <v>253</v>
@@ -7294,9 +7297,9 @@
       </c>
       <c r="N129" s="27"/>
     </row>
-    <row r="130" spans="1:14" ht="16.5" thickBot="1">
+    <row r="130" spans="1:14" ht="16.2" thickBot="1">
       <c r="A130" s="98"/>
-      <c r="B130" s="101" t="s">
+      <c r="B130" s="107" t="s">
         <v>182</v>
       </c>
       <c r="C130" s="7" t="s">
@@ -7310,9 +7313,9 @@
       </c>
       <c r="N130" s="25"/>
     </row>
-    <row r="131" spans="1:14" ht="16.5" thickBot="1">
+    <row r="131" spans="1:14" ht="16.2" thickBot="1">
       <c r="A131" s="98"/>
-      <c r="B131" s="101"/>
+      <c r="B131" s="107"/>
       <c r="C131" s="7" t="s">
         <v>185</v>
       </c>
@@ -7324,9 +7327,9 @@
       </c>
       <c r="N131" s="25"/>
     </row>
-    <row r="132" spans="1:14" ht="16.5" thickBot="1">
+    <row r="132" spans="1:14" ht="16.2" thickBot="1">
       <c r="A132" s="98"/>
-      <c r="B132" s="101"/>
+      <c r="B132" s="107"/>
       <c r="C132" s="7"/>
       <c r="D132" s="6" t="s">
         <v>215</v>
@@ -7336,7 +7339,7 @@
       </c>
       <c r="N132" s="28"/>
     </row>
-    <row r="133" spans="1:14" ht="16.5" thickBot="1">
+    <row r="133" spans="1:14" ht="16.2" thickBot="1">
       <c r="A133" s="98"/>
       <c r="B133" s="12" t="s">
         <v>255</v>
@@ -7352,7 +7355,7 @@
       </c>
       <c r="N133" s="28"/>
     </row>
-    <row r="134" spans="1:14" ht="16.5" thickBot="1">
+    <row r="134" spans="1:14" ht="16.2" thickBot="1">
       <c r="A134" s="98"/>
       <c r="B134" s="17" t="s">
         <v>189</v>
@@ -7368,9 +7371,9 @@
       </c>
       <c r="N134" s="28"/>
     </row>
-    <row r="135" spans="1:14" ht="16.5" thickBot="1">
+    <row r="135" spans="1:14" ht="16.2" thickBot="1">
       <c r="A135" s="98"/>
-      <c r="B135" s="102" t="s">
+      <c r="B135" s="103" t="s">
         <v>254</v>
       </c>
       <c r="C135" s="6" t="s">
@@ -7384,9 +7387,9 @@
       </c>
       <c r="N135" s="25"/>
     </row>
-    <row r="136" spans="1:14" ht="15.75" thickBot="1">
+    <row r="136" spans="1:14" ht="15" thickBot="1">
       <c r="A136" s="98"/>
-      <c r="B136" s="102"/>
+      <c r="B136" s="103"/>
       <c r="C136" s="6" t="s">
         <v>185</v>
       </c>
@@ -7398,9 +7401,9 @@
       </c>
       <c r="N136" s="29"/>
     </row>
-    <row r="137" spans="1:14" ht="15.75" thickBot="1">
+    <row r="137" spans="1:14" ht="15" thickBot="1">
       <c r="A137" s="98"/>
-      <c r="B137" s="97" t="s">
+      <c r="B137" s="106" t="s">
         <v>785</v>
       </c>
       <c r="C137" s="17" t="s">
@@ -7416,7 +7419,7 @@
     </row>
     <row r="138" spans="1:14" ht="16.5" customHeight="1" thickBot="1">
       <c r="A138" s="98"/>
-      <c r="B138" s="97"/>
+      <c r="B138" s="106"/>
       <c r="E138" s="94" t="s">
         <v>783</v>
       </c>
@@ -7424,133 +7427,133 @@
     </row>
     <row r="139" spans="1:14" ht="16.5" customHeight="1" thickBot="1">
       <c r="A139" s="98"/>
-      <c r="B139" s="97"/>
+      <c r="B139" s="106"/>
       <c r="E139" s="94" t="s">
         <v>784</v>
       </c>
       <c r="N139" s="30"/>
     </row>
-    <row r="140" spans="1:14" ht="15.75" thickBot="1">
+    <row r="140" spans="1:14" ht="15" thickBot="1">
       <c r="N140" s="30"/>
     </row>
-    <row r="141" spans="1:14" ht="15.75" thickBot="1">
+    <row r="141" spans="1:14" ht="15" thickBot="1">
       <c r="N141" s="30"/>
     </row>
-    <row r="142" spans="1:14" ht="15.75" thickBot="1">
+    <row r="142" spans="1:14" ht="15" thickBot="1">
       <c r="N142" s="30"/>
     </row>
-    <row r="143" spans="1:14" ht="15.75" thickBot="1">
+    <row r="143" spans="1:14" ht="15" thickBot="1">
       <c r="N143" s="31"/>
     </row>
-    <row r="144" spans="1:14" ht="15.75" thickBot="1">
+    <row r="144" spans="1:14" ht="15" thickBot="1">
       <c r="N144" s="32"/>
     </row>
-    <row r="145" spans="14:14" ht="15.75" thickBot="1">
+    <row r="145" spans="14:14" ht="15" thickBot="1">
       <c r="N145" s="31"/>
     </row>
-    <row r="146" spans="14:14" ht="15.75" thickBot="1">
+    <row r="146" spans="14:14" ht="15" thickBot="1">
       <c r="N146" s="32"/>
     </row>
-    <row r="147" spans="14:14" ht="15.75" thickBot="1">
+    <row r="147" spans="14:14" ht="15" thickBot="1">
       <c r="N147" s="31"/>
     </row>
-    <row r="148" spans="14:14" ht="15.75" thickBot="1">
+    <row r="148" spans="14:14" ht="15" thickBot="1">
       <c r="N148" s="21"/>
     </row>
-    <row r="149" spans="14:14" ht="15.75" thickBot="1">
+    <row r="149" spans="14:14" ht="15" thickBot="1">
       <c r="N149" s="21"/>
     </row>
-    <row r="150" spans="14:14" ht="15.75" thickBot="1">
+    <row r="150" spans="14:14" ht="15" thickBot="1">
       <c r="N150" s="21"/>
     </row>
-    <row r="151" spans="14:14" ht="15.75" thickBot="1">
+    <row r="151" spans="14:14" ht="15" thickBot="1">
       <c r="N151" s="21"/>
     </row>
-    <row r="152" spans="14:14" ht="15.75" thickBot="1">
+    <row r="152" spans="14:14" ht="15" thickBot="1">
       <c r="N152" s="21"/>
     </row>
-    <row r="153" spans="14:14" ht="15.75" thickBot="1">
+    <row r="153" spans="14:14" ht="15" thickBot="1">
       <c r="N153" s="21"/>
     </row>
-    <row r="154" spans="14:14" ht="15.75" thickBot="1">
+    <row r="154" spans="14:14" ht="15" thickBot="1">
       <c r="N154" s="21"/>
     </row>
-    <row r="155" spans="14:14" ht="15.75" thickBot="1">
+    <row r="155" spans="14:14" ht="15" thickBot="1">
       <c r="N155" s="21"/>
     </row>
-    <row r="156" spans="14:14" ht="15.75" thickBot="1">
+    <row r="156" spans="14:14" ht="15" thickBot="1">
       <c r="N156" s="33"/>
     </row>
-    <row r="157" spans="14:14" ht="15.75" thickBot="1">
+    <row r="157" spans="14:14" ht="15" thickBot="1">
       <c r="N157" s="34"/>
     </row>
-    <row r="158" spans="14:14" ht="15.75" thickBot="1">
+    <row r="158" spans="14:14" ht="15" thickBot="1">
       <c r="N158" s="34"/>
     </row>
-    <row r="159" spans="14:14" ht="15.75" thickBot="1">
+    <row r="159" spans="14:14" ht="15" thickBot="1">
       <c r="N159" s="34"/>
     </row>
-    <row r="160" spans="14:14" ht="15.75" thickBot="1">
+    <row r="160" spans="14:14" ht="15" thickBot="1">
       <c r="N160" s="34"/>
     </row>
-    <row r="161" spans="14:14" ht="15.75" thickBot="1">
+    <row r="161" spans="14:14" ht="15" thickBot="1">
       <c r="N161" s="34"/>
     </row>
-    <row r="162" spans="14:14" ht="15.75" thickBot="1">
+    <row r="162" spans="14:14" ht="15" thickBot="1">
       <c r="N162" s="34"/>
     </row>
-    <row r="163" spans="14:14" ht="15.75" thickBot="1">
+    <row r="163" spans="14:14" ht="15" thickBot="1">
       <c r="N163" s="34"/>
     </row>
-    <row r="164" spans="14:14" ht="15.75" thickBot="1">
+    <row r="164" spans="14:14" ht="15" thickBot="1">
       <c r="N164" s="34"/>
     </row>
-    <row r="165" spans="14:14" ht="15.75" thickBot="1">
+    <row r="165" spans="14:14" ht="15" thickBot="1">
       <c r="N165" s="35"/>
     </row>
-    <row r="166" spans="14:14" ht="15.75" thickBot="1">
+    <row r="166" spans="14:14" ht="15" thickBot="1">
       <c r="N166" s="34"/>
     </row>
-    <row r="167" spans="14:14" ht="15.75" thickBot="1">
+    <row r="167" spans="14:14" ht="15" thickBot="1">
       <c r="N167" s="34"/>
     </row>
-    <row r="168" spans="14:14" ht="15.75" thickBot="1">
+    <row r="168" spans="14:14" ht="15" thickBot="1">
       <c r="N168" s="34"/>
     </row>
-    <row r="169" spans="14:14" ht="15.75" thickBot="1">
+    <row r="169" spans="14:14" ht="15" thickBot="1">
       <c r="N169" s="34"/>
     </row>
-    <row r="170" spans="14:14" ht="15.75" thickBot="1">
+    <row r="170" spans="14:14" ht="15" thickBot="1">
       <c r="N170" s="34"/>
     </row>
-    <row r="171" spans="14:14" ht="15.75" thickBot="1">
+    <row r="171" spans="14:14" ht="15" thickBot="1">
       <c r="N171" s="34"/>
     </row>
-    <row r="172" spans="14:14" ht="15.75" thickBot="1">
+    <row r="172" spans="14:14" ht="15" thickBot="1">
       <c r="N172" s="34"/>
     </row>
-    <row r="173" spans="14:14" ht="15.75" thickBot="1">
+    <row r="173" spans="14:14" ht="15" thickBot="1">
       <c r="N173" s="34"/>
     </row>
-    <row r="174" spans="14:14" ht="15.75" thickBot="1">
+    <row r="174" spans="14:14" ht="15" thickBot="1">
       <c r="N174" s="35"/>
     </row>
-    <row r="175" spans="14:14" ht="15.75" thickBot="1">
+    <row r="175" spans="14:14" ht="15" thickBot="1">
       <c r="N175" s="35"/>
     </row>
-    <row r="176" spans="14:14" ht="15.75" thickBot="1">
+    <row r="176" spans="14:14" ht="15" thickBot="1">
       <c r="N176" s="34"/>
     </row>
-    <row r="177" spans="14:14" ht="15.75" thickBot="1">
+    <row r="177" spans="14:14" ht="15" thickBot="1">
       <c r="N177" s="34"/>
     </row>
-    <row r="178" spans="14:14" ht="15.75" thickBot="1">
+    <row r="178" spans="14:14" ht="15" thickBot="1">
       <c r="N178" s="34"/>
     </row>
-    <row r="179" spans="14:14" ht="15.75" thickBot="1">
+    <row r="179" spans="14:14" ht="15" thickBot="1">
       <c r="N179" s="34"/>
     </row>
-    <row r="180" spans="14:14" ht="15.75" thickBot="1">
+    <row r="180" spans="14:14" ht="15" thickBot="1">
       <c r="N180" s="34"/>
     </row>
   </sheetData>
@@ -7561,16 +7564,13 @@
     </dataRefs>
   </dataConsolidate>
   <mergeCells count="32">
-    <mergeCell ref="B2:B10"/>
-    <mergeCell ref="A2:A47"/>
-    <mergeCell ref="B11:B17"/>
-    <mergeCell ref="B18:B23"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="B36:B39"/>
-    <mergeCell ref="B40:B43"/>
-    <mergeCell ref="B44:B47"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="A121:A139"/>
+    <mergeCell ref="B121:B122"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="B130:B132"/>
+    <mergeCell ref="B135:B136"/>
     <mergeCell ref="B87:B91"/>
     <mergeCell ref="B93:B95"/>
     <mergeCell ref="B96:B99"/>
@@ -7586,13 +7586,16 @@
     <mergeCell ref="B104:B108"/>
     <mergeCell ref="B109:B110"/>
     <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="A121:A139"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="B124:B125"/>
-    <mergeCell ref="B126:B127"/>
-    <mergeCell ref="B130:B132"/>
-    <mergeCell ref="B135:B136"/>
+    <mergeCell ref="B2:B10"/>
+    <mergeCell ref="A2:A47"/>
+    <mergeCell ref="B11:B17"/>
+    <mergeCell ref="B18:B23"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="B40:B43"/>
+    <mergeCell ref="B44:B47"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7604,19 +7607,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF384FCC-53C0-4210-88B7-08AF18C43962}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:K85"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.69921875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="30.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>799</v>
       </c>
@@ -8777,18 +8780,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5034112D-A02C-48A9-B69E-FD66096D0F2F}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:L306"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.25" customWidth="1"/>
-    <col min="4" max="4" width="23.25" customWidth="1"/>
-    <col min="6" max="6" width="15.125" customWidth="1"/>
+    <col min="1" max="1" width="20.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.19921875" customWidth="1"/>
+    <col min="4" max="4" width="23.19921875" customWidth="1"/>
+    <col min="6" max="6" width="15.09765625" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="31.625" customWidth="1"/>
+    <col min="9" max="9" width="31.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1">
+    <row r="1" spans="1:12" ht="15" thickBot="1">
       <c r="A1" t="s">
         <v>376</v>
       </c>
@@ -8814,11 +8817,11 @@
         <v>256</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A2" s="100" t="s">
+    <row r="2" spans="1:12" ht="15" thickBot="1">
+      <c r="A2" s="102" t="s">
         <v>378</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="106" t="s">
         <v>560</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -8840,9 +8843,9 @@
         <v>458</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A3" s="100"/>
-      <c r="B3" s="97"/>
+    <row r="3" spans="1:12" ht="15" thickBot="1">
+      <c r="A3" s="102"/>
+      <c r="B3" s="106"/>
       <c r="C3" s="4" t="s">
         <v>389</v>
       </c>
@@ -8862,9 +8865,9 @@
         <v>459</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A4" s="100"/>
-      <c r="B4" s="97"/>
+    <row r="4" spans="1:12" ht="15" thickBot="1">
+      <c r="A4" s="102"/>
+      <c r="B4" s="106"/>
       <c r="C4" s="4" t="s">
         <v>390</v>
       </c>
@@ -8887,9 +8890,9 @@
         <v>377</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A5" s="100"/>
-      <c r="B5" s="97"/>
+    <row r="5" spans="1:12" ht="15" thickBot="1">
+      <c r="A5" s="102"/>
+      <c r="B5" s="106"/>
       <c r="C5" s="4" t="s">
         <v>391</v>
       </c>
@@ -8912,9 +8915,9 @@
         <v>557</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A6" s="100"/>
-      <c r="B6" s="97"/>
+    <row r="6" spans="1:12" ht="15" thickBot="1">
+      <c r="A6" s="102"/>
+      <c r="B6" s="106"/>
       <c r="C6" s="4" t="s">
         <v>392</v>
       </c>
@@ -8937,8 +8940,8 @@
         <v>379</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A7" s="100"/>
+    <row r="7" spans="1:12" ht="15" thickBot="1">
+      <c r="A7" s="102"/>
       <c r="B7" s="67"/>
       <c r="C7" s="4" t="s">
         <v>215</v>
@@ -8959,8 +8962,8 @@
         <v>463</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A8" s="100"/>
+    <row r="8" spans="1:12" ht="15" thickBot="1">
+      <c r="A8" s="102"/>
       <c r="B8" s="113" t="s">
         <v>561</v>
       </c>
@@ -8983,8 +8986,8 @@
         <v>464</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A9" s="100"/>
+    <row r="9" spans="1:12" ht="15" thickBot="1">
+      <c r="A9" s="102"/>
       <c r="B9" s="113"/>
       <c r="C9" s="6" t="s">
         <v>395</v>
@@ -9002,8 +9005,8 @@
         <v>465</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A10" s="100"/>
+    <row r="10" spans="1:12" ht="15" thickBot="1">
+      <c r="A10" s="102"/>
       <c r="B10" s="113"/>
       <c r="C10" s="6" t="s">
         <v>396</v>
@@ -9021,8 +9024,8 @@
         <v>466</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A11" s="100"/>
+    <row r="11" spans="1:12" ht="15" thickBot="1">
+      <c r="A11" s="102"/>
       <c r="B11" s="68"/>
       <c r="C11" s="6" t="s">
         <v>215</v>
@@ -9040,9 +9043,9 @@
         <v>467</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A12" s="100"/>
-      <c r="B12" s="97" t="s">
+    <row r="12" spans="1:12" ht="15" thickBot="1">
+      <c r="A12" s="102"/>
+      <c r="B12" s="106" t="s">
         <v>565</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -9061,9 +9064,9 @@
         <v>542</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A13" s="100"/>
-      <c r="B13" s="97"/>
+    <row r="13" spans="1:12" ht="15" thickBot="1">
+      <c r="A13" s="102"/>
+      <c r="B13" s="106"/>
       <c r="C13" s="7" t="s">
         <v>401</v>
       </c>
@@ -9080,9 +9083,9 @@
         <v>543</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A14" s="100"/>
-      <c r="B14" s="97"/>
+    <row r="14" spans="1:12" ht="15" thickBot="1">
+      <c r="A14" s="102"/>
+      <c r="B14" s="106"/>
       <c r="C14" s="7" t="s">
         <v>402</v>
       </c>
@@ -9099,9 +9102,9 @@
         <v>469</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A15" s="100"/>
-      <c r="B15" s="97"/>
+    <row r="15" spans="1:12" ht="15" thickBot="1">
+      <c r="A15" s="102"/>
+      <c r="B15" s="106"/>
       <c r="C15" s="7" t="s">
         <v>403</v>
       </c>
@@ -9118,9 +9121,9 @@
         <v>470</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A16" s="100"/>
-      <c r="B16" s="97"/>
+    <row r="16" spans="1:12" ht="15" thickBot="1">
+      <c r="A16" s="102"/>
+      <c r="B16" s="106"/>
       <c r="C16" s="7" t="s">
         <v>404</v>
       </c>
@@ -9135,9 +9138,9 @@
         <v>471</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A17" s="100"/>
-      <c r="B17" s="97"/>
+    <row r="17" spans="1:9" ht="15" thickBot="1">
+      <c r="A17" s="102"/>
+      <c r="B17" s="106"/>
       <c r="C17" s="7" t="s">
         <v>405</v>
       </c>
@@ -9152,8 +9155,8 @@
         <v>472</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A18" s="100"/>
+    <row r="18" spans="1:9" ht="15" thickBot="1">
+      <c r="A18" s="102"/>
       <c r="B18" s="67"/>
       <c r="C18" s="7" t="s">
         <v>215</v>
@@ -9169,8 +9172,8 @@
         <v>473</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A19" s="100"/>
+    <row r="19" spans="1:9" ht="15" thickBot="1">
+      <c r="A19" s="102"/>
       <c r="B19" s="114" t="s">
         <v>562</v>
       </c>
@@ -9190,8 +9193,8 @@
         <v>474</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A20" s="100"/>
+    <row r="20" spans="1:9" ht="15" thickBot="1">
+      <c r="A20" s="102"/>
       <c r="B20" s="114"/>
       <c r="C20" s="6" t="s">
         <v>420</v>
@@ -9207,8 +9210,8 @@
         <v>475</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A21" s="100"/>
+    <row r="21" spans="1:9" ht="15" thickBot="1">
+      <c r="A21" s="102"/>
       <c r="B21" s="114"/>
       <c r="C21" s="6" t="s">
         <v>421</v>
@@ -9224,8 +9227,8 @@
         <v>544</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A22" s="100"/>
+    <row r="22" spans="1:9" ht="15" thickBot="1">
+      <c r="A22" s="102"/>
       <c r="B22" s="69"/>
       <c r="C22" s="6" t="s">
         <v>215</v>
@@ -9241,8 +9244,8 @@
         <v>477</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A23" s="100"/>
+    <row r="23" spans="1:9" ht="15" thickBot="1">
+      <c r="A23" s="102"/>
       <c r="B23" s="110" t="s">
         <v>563</v>
       </c>
@@ -9262,8 +9265,8 @@
         <v>478</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A24" s="100"/>
+    <row r="24" spans="1:9" ht="15" thickBot="1">
+      <c r="A24" s="102"/>
       <c r="B24" s="110"/>
       <c r="C24" s="4"/>
       <c r="D24" s="7" t="s">
@@ -9276,8 +9279,8 @@
         <v>479</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A25" s="100"/>
+    <row r="25" spans="1:9" ht="15" thickBot="1">
+      <c r="A25" s="102"/>
       <c r="B25" s="110"/>
       <c r="C25" s="4"/>
       <c r="D25" s="7" t="s">
@@ -9290,8 +9293,8 @@
         <v>480</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A26" s="100"/>
+    <row r="26" spans="1:9" ht="15" thickBot="1">
+      <c r="A26" s="102"/>
       <c r="B26" s="114" t="s">
         <v>381</v>
       </c>
@@ -9308,8 +9311,8 @@
         <v>481</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A27" s="100"/>
+    <row r="27" spans="1:9" ht="15" thickBot="1">
+      <c r="A27" s="102"/>
       <c r="B27" s="114"/>
       <c r="C27" s="6" t="s">
         <v>426</v>
@@ -9322,8 +9325,8 @@
         <v>267</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A28" s="100"/>
+    <row r="28" spans="1:9" ht="15" thickBot="1">
+      <c r="A28" s="102"/>
       <c r="B28" s="69"/>
       <c r="C28" s="6" t="s">
         <v>215</v>
@@ -9336,8 +9339,8 @@
         <v>268</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A29" s="100"/>
+    <row r="29" spans="1:9" ht="15" thickBot="1">
+      <c r="A29" s="102"/>
       <c r="B29" s="40" t="s">
         <v>382</v>
       </c>
@@ -9354,8 +9357,8 @@
         <v>482</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A30" s="100"/>
+    <row r="30" spans="1:9" ht="15" thickBot="1">
+      <c r="A30" s="102"/>
       <c r="B30" s="47" t="s">
         <v>558</v>
       </c>
@@ -9372,8 +9375,8 @@
         <v>468</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A31" s="100"/>
+    <row r="31" spans="1:9" ht="15" thickBot="1">
+      <c r="A31" s="102"/>
       <c r="B31" s="40" t="s">
         <v>559</v>
       </c>
@@ -9390,8 +9393,8 @@
         <v>483</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A32" s="100"/>
+    <row r="32" spans="1:9" ht="15" thickBot="1">
+      <c r="A32" s="102"/>
       <c r="B32" s="47" t="s">
         <v>383</v>
       </c>
@@ -9408,8 +9411,8 @@
         <v>484</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A33" s="100"/>
+    <row r="33" spans="1:9" ht="15" thickBot="1">
+      <c r="A33" s="102"/>
       <c r="B33" s="40" t="s">
         <v>384</v>
       </c>
@@ -9426,8 +9429,8 @@
         <v>485</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A34" s="100"/>
+    <row r="34" spans="1:9" ht="15" thickBot="1">
+      <c r="A34" s="102"/>
       <c r="B34" s="6" t="s">
         <v>385</v>
       </c>
@@ -9444,9 +9447,9 @@
         <v>486</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A35" s="100"/>
-      <c r="B35" s="101" t="s">
+    <row r="35" spans="1:9" ht="15" thickBot="1">
+      <c r="A35" s="102"/>
+      <c r="B35" s="107" t="s">
         <v>564</v>
       </c>
       <c r="C35" s="7" t="s">
@@ -9459,9 +9462,9 @@
         <v>487</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A36" s="100"/>
-      <c r="B36" s="101"/>
+    <row r="36" spans="1:9" ht="15" thickBot="1">
+      <c r="A36" s="102"/>
+      <c r="B36" s="107"/>
       <c r="C36" s="7" t="s">
         <v>413</v>
       </c>
@@ -9472,9 +9475,9 @@
         <v>488</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A37" s="100"/>
-      <c r="B37" s="101"/>
+    <row r="37" spans="1:9" ht="15" thickBot="1">
+      <c r="A37" s="102"/>
+      <c r="B37" s="107"/>
       <c r="C37" s="7" t="s">
         <v>414</v>
       </c>
@@ -9485,9 +9488,9 @@
         <v>489</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A38" s="100"/>
-      <c r="B38" s="101"/>
+    <row r="38" spans="1:9" ht="15" thickBot="1">
+      <c r="A38" s="102"/>
+      <c r="B38" s="107"/>
       <c r="C38" s="7" t="s">
         <v>415</v>
       </c>
@@ -9498,8 +9501,8 @@
         <v>490</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A39" s="100"/>
+    <row r="39" spans="1:9" ht="15" thickBot="1">
+      <c r="A39" s="102"/>
       <c r="B39" s="64"/>
       <c r="C39" s="7" t="s">
         <v>215</v>
@@ -9509,8 +9512,8 @@
         <v>491</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A40" s="100"/>
+    <row r="40" spans="1:9" ht="15" thickBot="1">
+      <c r="A40" s="102"/>
       <c r="B40" s="6" t="s">
         <v>255</v>
       </c>
@@ -9524,7 +9527,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" thickBot="1">
+    <row r="41" spans="1:9" ht="15" thickBot="1">
       <c r="A41" s="8"/>
       <c r="B41" s="108" t="s">
         <v>798</v>
@@ -9539,7 +9542,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" thickBot="1">
+    <row r="42" spans="1:9" ht="15" thickBot="1">
       <c r="A42" s="8"/>
       <c r="B42" s="108"/>
       <c r="C42" s="4" t="s">
@@ -9552,7 +9555,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" thickBot="1">
+    <row r="43" spans="1:9" ht="15" thickBot="1">
       <c r="A43" s="8"/>
       <c r="B43" s="108"/>
       <c r="C43" s="4" t="s">
@@ -9565,7 +9568,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" thickBot="1">
+    <row r="44" spans="1:9" ht="15" thickBot="1">
       <c r="A44" s="8"/>
       <c r="B44" s="63"/>
       <c r="C44" s="4"/>
@@ -9576,7 +9579,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.75" thickBot="1">
+    <row r="45" spans="1:9" ht="15" thickBot="1">
       <c r="A45" s="8"/>
       <c r="B45" s="63"/>
       <c r="C45" s="4"/>
@@ -9587,7 +9590,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" thickBot="1">
+    <row r="46" spans="1:9" ht="15" thickBot="1">
       <c r="A46" s="8"/>
       <c r="B46" s="63"/>
       <c r="C46" s="4"/>
@@ -9598,7 +9601,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.75" thickBot="1">
+    <row r="47" spans="1:9" ht="15" thickBot="1">
       <c r="A47" s="8"/>
       <c r="B47" s="63"/>
       <c r="C47" s="4"/>
@@ -9609,7 +9612,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" thickBot="1">
+    <row r="48" spans="1:9" ht="15" thickBot="1">
       <c r="A48" s="8"/>
       <c r="B48" s="63"/>
       <c r="C48" s="4"/>
@@ -9620,7 +9623,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.75" thickBot="1">
+    <row r="49" spans="1:9" ht="15" thickBot="1">
       <c r="A49" s="8"/>
       <c r="B49" s="63"/>
       <c r="C49" s="4"/>
@@ -9631,7 +9634,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.75" thickBot="1">
+    <row r="50" spans="1:9" ht="15" thickBot="1">
       <c r="A50" s="8"/>
       <c r="B50" s="63"/>
       <c r="C50" s="4"/>
@@ -9642,8 +9645,8 @@
         <v>502</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A51" s="99" t="s">
+    <row r="51" spans="1:9" ht="15" thickBot="1">
+      <c r="A51" s="104" t="s">
         <v>377</v>
       </c>
       <c r="B51" s="110" t="s">
@@ -9659,8 +9662,8 @@
         <v>503</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A52" s="99"/>
+    <row r="52" spans="1:9" ht="15" thickBot="1">
+      <c r="A52" s="104"/>
       <c r="B52" s="110"/>
       <c r="C52" s="4"/>
       <c r="D52" s="7" t="s">
@@ -9670,8 +9673,8 @@
         <v>269</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A53" s="99"/>
+    <row r="53" spans="1:9" ht="15" thickBot="1">
+      <c r="A53" s="104"/>
       <c r="B53" s="110"/>
       <c r="C53" s="4"/>
       <c r="D53" s="7" t="s">
@@ -9681,7 +9684,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.75" thickBot="1">
+    <row r="54" spans="1:9" ht="15" thickBot="1">
       <c r="A54" s="57"/>
       <c r="B54" s="66"/>
       <c r="C54" s="4"/>
@@ -9692,7 +9695,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" thickBot="1">
+    <row r="55" spans="1:9" ht="15" thickBot="1">
       <c r="A55" s="41" t="s">
         <v>379</v>
       </c>
@@ -9709,187 +9712,187 @@
         <v>504</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.75" thickBot="1">
+    <row r="56" spans="1:9" ht="15" thickBot="1">
       <c r="I56" s="21" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.75" thickBot="1">
+    <row r="57" spans="1:9" ht="15" thickBot="1">
       <c r="I57" s="21" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.75" thickBot="1">
+    <row r="58" spans="1:9" ht="15" thickBot="1">
       <c r="I58" s="21" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" thickBot="1">
+    <row r="59" spans="1:9" ht="15" thickBot="1">
       <c r="I59" s="21" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.75" thickBot="1">
+    <row r="60" spans="1:9" ht="15" thickBot="1">
       <c r="I60" s="43" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" thickBot="1">
+    <row r="61" spans="1:9" ht="15" thickBot="1">
       <c r="I61" s="44" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.75" thickBot="1">
+    <row r="62" spans="1:9" ht="15" thickBot="1">
       <c r="I62" s="21" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.75" thickBot="1">
+    <row r="63" spans="1:9" ht="15" thickBot="1">
       <c r="I63" s="21" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.75" thickBot="1">
+    <row r="64" spans="1:9" ht="15" thickBot="1">
       <c r="I64" s="21" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="65" spans="9:9" ht="15.75" thickBot="1">
+    <row r="65" spans="9:9" ht="15" thickBot="1">
       <c r="I65" s="43" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="66" spans="9:9" ht="15.75" thickBot="1">
+    <row r="66" spans="9:9" ht="15" thickBot="1">
       <c r="I66" s="21" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="67" spans="9:9" ht="15.75" thickBot="1">
+    <row r="67" spans="9:9" ht="15" thickBot="1">
       <c r="I67" s="21" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="68" spans="9:9" ht="15.75" thickBot="1">
+    <row r="68" spans="9:9" ht="15" thickBot="1">
       <c r="I68" s="21" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="69" spans="9:9" ht="15.75" thickBot="1">
+    <row r="69" spans="9:9" ht="15" thickBot="1">
       <c r="I69" s="21" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="70" spans="9:9" ht="15.75" thickBot="1">
+    <row r="70" spans="9:9" ht="15" thickBot="1">
       <c r="I70" s="21" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="71" spans="9:9" ht="15.75" thickBot="1">
+    <row r="71" spans="9:9" ht="15" thickBot="1">
       <c r="I71" s="21" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="72" spans="9:9" ht="15.75" thickBot="1">
+    <row r="72" spans="9:9" ht="15" thickBot="1">
       <c r="I72" s="21" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="73" spans="9:9" ht="15.75" thickBot="1">
+    <row r="73" spans="9:9" ht="15" thickBot="1">
       <c r="I73" s="21" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="74" spans="9:9" ht="15.75" thickBot="1">
+    <row r="74" spans="9:9" ht="15" thickBot="1">
       <c r="I74" s="21" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="75" spans="9:9" ht="15" thickBot="1">
+    <row r="75" spans="9:9" ht="14.4" thickBot="1">
       <c r="I75" s="45" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="76" spans="9:9" ht="15.75" thickBot="1">
+    <row r="76" spans="9:9" ht="15" thickBot="1">
       <c r="I76" s="21" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="77" spans="9:9" ht="15.75" thickBot="1">
+    <row r="77" spans="9:9" ht="15" thickBot="1">
       <c r="I77" s="21" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="78" spans="9:9" ht="15.75" thickBot="1">
+    <row r="78" spans="9:9" ht="15" thickBot="1">
       <c r="I78" s="21" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="79" spans="9:9" ht="15.75" thickBot="1">
+    <row r="79" spans="9:9" ht="15" thickBot="1">
       <c r="I79" s="21" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="80" spans="9:9" ht="15.75" thickBot="1">
+    <row r="80" spans="9:9" ht="15" thickBot="1">
       <c r="I80" s="30" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="81" spans="9:9" ht="15.75" thickBot="1">
+    <row r="81" spans="9:9" ht="15" thickBot="1">
       <c r="I81" s="21" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="82" spans="9:9" ht="15.75" thickBot="1">
+    <row r="82" spans="9:9" ht="15" thickBot="1">
       <c r="I82" s="21" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="83" spans="9:9" ht="15.75" thickBot="1">
+    <row r="83" spans="9:9" ht="15" thickBot="1">
       <c r="I83" s="21" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="84" spans="9:9" ht="15.75" thickBot="1">
+    <row r="84" spans="9:9" ht="15" thickBot="1">
       <c r="I84" s="21" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="85" spans="9:9" ht="15.75" thickBot="1">
+    <row r="85" spans="9:9" ht="15" thickBot="1">
       <c r="I85" s="21" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="86" spans="9:9" ht="15.75" thickBot="1">
+    <row r="86" spans="9:9" ht="15" thickBot="1">
       <c r="I86" s="21" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="87" spans="9:9" ht="15.75" thickBot="1">
+    <row r="87" spans="9:9" ht="15" thickBot="1">
       <c r="I87" s="21" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="88" spans="9:9" ht="15.75" thickBot="1">
+    <row r="88" spans="9:9" ht="15" thickBot="1">
       <c r="I88" s="21" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="89" spans="9:9" ht="15" thickBot="1">
+    <row r="89" spans="9:9" ht="14.4" thickBot="1">
       <c r="I89" s="36" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="90" spans="9:9" ht="15" thickBot="1">
+    <row r="90" spans="9:9" ht="14.4" thickBot="1">
       <c r="I90" s="36" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="91" spans="9:9" ht="15" thickBot="1">
+    <row r="91" spans="9:9" ht="14.4" thickBot="1">
       <c r="I91" s="36" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="92" spans="9:9" ht="15" thickBot="1">
+    <row r="92" spans="9:9" ht="14.4" thickBot="1">
       <c r="I92" s="36" t="s">
         <v>540</v>
       </c>
@@ -9899,651 +9902,651 @@
         <v>541</v>
       </c>
     </row>
-    <row r="94" spans="9:9" ht="15" thickBot="1">
+    <row r="94" spans="9:9" ht="14.4" thickBot="1">
       <c r="I94" s="112"/>
     </row>
-    <row r="97" spans="9:9" ht="15" thickBot="1"/>
-    <row r="98" spans="9:9" ht="15.75" thickBot="1">
+    <row r="97" spans="9:9" ht="14.4" thickBot="1"/>
+    <row r="98" spans="9:9" ht="15" thickBot="1">
       <c r="I98" s="46"/>
     </row>
-    <row r="99" spans="9:9" ht="15.75" thickBot="1">
+    <row r="99" spans="9:9" ht="15" thickBot="1">
       <c r="I99" s="46"/>
     </row>
-    <row r="100" spans="9:9" ht="15.75" thickBot="1">
+    <row r="100" spans="9:9" ht="15" thickBot="1">
       <c r="I100" s="46"/>
     </row>
-    <row r="101" spans="9:9" ht="15.75" thickBot="1">
+    <row r="101" spans="9:9" ht="15" thickBot="1">
       <c r="I101" s="46"/>
     </row>
-    <row r="102" spans="9:9" ht="15.75" thickBot="1">
+    <row r="102" spans="9:9" ht="15" thickBot="1">
       <c r="I102" s="46"/>
     </row>
-    <row r="103" spans="9:9" ht="15.75" thickBot="1">
+    <row r="103" spans="9:9" ht="15" thickBot="1">
       <c r="I103" s="46"/>
     </row>
-    <row r="104" spans="9:9" ht="15.75" thickBot="1">
+    <row r="104" spans="9:9" ht="15" thickBot="1">
       <c r="I104" s="46"/>
     </row>
-    <row r="105" spans="9:9" ht="15.75" thickBot="1">
+    <row r="105" spans="9:9" ht="15" thickBot="1">
       <c r="I105" s="46"/>
     </row>
-    <row r="106" spans="9:9" ht="15.75" thickBot="1">
+    <row r="106" spans="9:9" ht="15" thickBot="1">
       <c r="I106" s="46"/>
     </row>
-    <row r="107" spans="9:9" ht="15.75" thickBot="1">
+    <row r="107" spans="9:9" ht="15" thickBot="1">
       <c r="I107" s="46"/>
     </row>
-    <row r="108" spans="9:9" ht="15.75" thickBot="1">
+    <row r="108" spans="9:9" ht="15" thickBot="1">
       <c r="I108" s="46"/>
     </row>
-    <row r="109" spans="9:9" ht="15.75" thickBot="1">
+    <row r="109" spans="9:9" ht="15" thickBot="1">
       <c r="I109" s="46"/>
     </row>
-    <row r="110" spans="9:9" ht="15.75" thickBot="1">
+    <row r="110" spans="9:9" ht="15" thickBot="1">
       <c r="I110" s="46"/>
     </row>
-    <row r="111" spans="9:9" ht="15.75" thickBot="1">
+    <row r="111" spans="9:9" ht="15" thickBot="1">
       <c r="I111" s="46"/>
     </row>
-    <row r="112" spans="9:9" ht="15.75" thickBot="1">
+    <row r="112" spans="9:9" ht="15" thickBot="1">
       <c r="I112" s="46"/>
     </row>
-    <row r="113" spans="9:9" ht="15.75" thickBot="1">
+    <row r="113" spans="9:9" ht="15" thickBot="1">
       <c r="I113" s="46"/>
     </row>
-    <row r="114" spans="9:9" ht="15.75" thickBot="1">
+    <row r="114" spans="9:9" ht="15" thickBot="1">
       <c r="I114" s="46"/>
     </row>
-    <row r="115" spans="9:9" ht="15.75" thickBot="1">
+    <row r="115" spans="9:9" ht="15" thickBot="1">
       <c r="I115" s="46"/>
     </row>
-    <row r="116" spans="9:9" ht="15.75" thickBot="1">
+    <row r="116" spans="9:9" ht="15" thickBot="1">
       <c r="I116" s="46"/>
     </row>
-    <row r="117" spans="9:9" ht="15.75" thickBot="1">
+    <row r="117" spans="9:9" ht="15" thickBot="1">
       <c r="I117" s="46"/>
     </row>
-    <row r="118" spans="9:9" ht="15.75" thickBot="1">
+    <row r="118" spans="9:9" ht="15" thickBot="1">
       <c r="I118" s="46"/>
     </row>
-    <row r="119" spans="9:9" ht="15.75" thickBot="1">
+    <row r="119" spans="9:9" ht="15" thickBot="1">
       <c r="I119" s="46"/>
     </row>
-    <row r="120" spans="9:9" ht="15.75" thickBot="1">
+    <row r="120" spans="9:9" ht="15" thickBot="1">
       <c r="I120" s="46"/>
     </row>
-    <row r="121" spans="9:9" ht="15.75" thickBot="1">
+    <row r="121" spans="9:9" ht="15" thickBot="1">
       <c r="I121" s="46"/>
     </row>
-    <row r="122" spans="9:9" ht="15.75" thickBot="1">
+    <row r="122" spans="9:9" ht="15" thickBot="1">
       <c r="I122" s="46"/>
     </row>
-    <row r="123" spans="9:9" ht="15.75" thickBot="1">
+    <row r="123" spans="9:9" ht="15" thickBot="1">
       <c r="I123" s="46"/>
     </row>
-    <row r="124" spans="9:9" ht="15.75" thickBot="1">
+    <row r="124" spans="9:9" ht="15" thickBot="1">
       <c r="I124" s="46"/>
     </row>
-    <row r="125" spans="9:9" ht="15.75" thickBot="1">
+    <row r="125" spans="9:9" ht="15" thickBot="1">
       <c r="I125" s="46"/>
     </row>
-    <row r="126" spans="9:9" ht="15.75" thickBot="1">
+    <row r="126" spans="9:9" ht="15" thickBot="1">
       <c r="I126" s="46"/>
     </row>
-    <row r="127" spans="9:9" ht="15.75" thickBot="1">
+    <row r="127" spans="9:9" ht="15" thickBot="1">
       <c r="I127" s="46"/>
     </row>
-    <row r="128" spans="9:9" ht="15.75" thickBot="1">
+    <row r="128" spans="9:9" ht="15" thickBot="1">
       <c r="I128" s="46"/>
     </row>
-    <row r="129" spans="9:9" ht="15.75" thickBot="1">
+    <row r="129" spans="9:9" ht="15" thickBot="1">
       <c r="I129" s="46"/>
     </row>
-    <row r="130" spans="9:9" ht="15.75" thickBot="1">
+    <row r="130" spans="9:9" ht="15" thickBot="1">
       <c r="I130" s="46"/>
     </row>
-    <row r="131" spans="9:9" ht="15.75" thickBot="1">
+    <row r="131" spans="9:9" ht="15" thickBot="1">
       <c r="I131" s="46"/>
     </row>
-    <row r="132" spans="9:9" ht="15.75" thickBot="1">
+    <row r="132" spans="9:9" ht="15" thickBot="1">
       <c r="I132" s="46"/>
     </row>
-    <row r="133" spans="9:9" ht="15.75" thickBot="1">
+    <row r="133" spans="9:9" ht="15" thickBot="1">
       <c r="I133" s="46"/>
     </row>
-    <row r="134" spans="9:9" ht="15.75" thickBot="1">
+    <row r="134" spans="9:9" ht="15" thickBot="1">
       <c r="I134" s="46"/>
     </row>
-    <row r="135" spans="9:9" ht="15.75" thickBot="1">
+    <row r="135" spans="9:9" ht="15" thickBot="1">
       <c r="I135" s="46"/>
     </row>
-    <row r="136" spans="9:9" ht="15.75" thickBot="1">
+    <row r="136" spans="9:9" ht="15" thickBot="1">
       <c r="I136" s="46"/>
     </row>
-    <row r="137" spans="9:9" ht="15.75" thickBot="1">
+    <row r="137" spans="9:9" ht="15" thickBot="1">
       <c r="I137" s="46"/>
     </row>
-    <row r="138" spans="9:9" ht="15.75" thickBot="1">
+    <row r="138" spans="9:9" ht="15" thickBot="1">
       <c r="I138" s="46"/>
     </row>
-    <row r="139" spans="9:9" ht="15.75" thickBot="1">
+    <row r="139" spans="9:9" ht="15" thickBot="1">
       <c r="I139" s="46"/>
     </row>
-    <row r="140" spans="9:9" ht="15.75" thickBot="1">
+    <row r="140" spans="9:9" ht="15" thickBot="1">
       <c r="I140" s="46"/>
     </row>
-    <row r="141" spans="9:9" ht="15.75" thickBot="1">
+    <row r="141" spans="9:9" ht="15" thickBot="1">
       <c r="I141" s="46"/>
     </row>
-    <row r="142" spans="9:9" ht="15.75" thickBot="1">
+    <row r="142" spans="9:9" ht="15" thickBot="1">
       <c r="I142" s="46"/>
     </row>
-    <row r="143" spans="9:9" ht="15.75" thickBot="1">
+    <row r="143" spans="9:9" ht="15" thickBot="1">
       <c r="I143" s="46"/>
     </row>
-    <row r="144" spans="9:9" ht="15.75" thickBot="1">
+    <row r="144" spans="9:9" ht="15" thickBot="1">
       <c r="I144" s="46"/>
     </row>
-    <row r="145" spans="9:9" ht="15.75" thickBot="1">
+    <row r="145" spans="9:9" ht="15" thickBot="1">
       <c r="I145" s="46"/>
     </row>
-    <row r="146" spans="9:9" ht="15.75" thickBot="1">
+    <row r="146" spans="9:9" ht="15" thickBot="1">
       <c r="I146" s="46"/>
     </row>
-    <row r="147" spans="9:9" ht="15.75" thickBot="1">
+    <row r="147" spans="9:9" ht="15" thickBot="1">
       <c r="I147" s="46"/>
     </row>
-    <row r="148" spans="9:9" ht="15.75" thickBot="1">
+    <row r="148" spans="9:9" ht="15" thickBot="1">
       <c r="I148" s="46"/>
     </row>
-    <row r="149" spans="9:9" ht="15.75" thickBot="1">
+    <row r="149" spans="9:9" ht="15" thickBot="1">
       <c r="I149" s="46"/>
     </row>
-    <row r="150" spans="9:9" ht="15.75" thickBot="1">
+    <row r="150" spans="9:9" ht="15" thickBot="1">
       <c r="I150" s="46"/>
     </row>
-    <row r="151" spans="9:9" ht="15.75" thickBot="1">
+    <row r="151" spans="9:9" ht="15" thickBot="1">
       <c r="I151" s="46"/>
     </row>
-    <row r="152" spans="9:9" ht="15.75" thickBot="1">
+    <row r="152" spans="9:9" ht="15" thickBot="1">
       <c r="I152" s="46"/>
     </row>
-    <row r="153" spans="9:9" ht="15.75" thickBot="1">
+    <row r="153" spans="9:9" ht="15" thickBot="1">
       <c r="I153" s="46"/>
     </row>
-    <row r="154" spans="9:9" ht="15.75" thickBot="1">
+    <row r="154" spans="9:9" ht="15" thickBot="1">
       <c r="I154" s="46"/>
     </row>
-    <row r="155" spans="9:9" ht="15.75" thickBot="1">
+    <row r="155" spans="9:9" ht="15" thickBot="1">
       <c r="I155" s="46"/>
     </row>
-    <row r="156" spans="9:9" ht="15.75" thickBot="1">
+    <row r="156" spans="9:9" ht="15" thickBot="1">
       <c r="I156" s="46"/>
     </row>
-    <row r="157" spans="9:9" ht="15.75" thickBot="1">
+    <row r="157" spans="9:9" ht="15" thickBot="1">
       <c r="I157" s="46"/>
     </row>
-    <row r="158" spans="9:9" ht="15.75" thickBot="1">
+    <row r="158" spans="9:9" ht="15" thickBot="1">
       <c r="I158" s="46"/>
     </row>
-    <row r="159" spans="9:9" ht="15.75" thickBot="1">
+    <row r="159" spans="9:9" ht="15" thickBot="1">
       <c r="I159" s="46"/>
     </row>
-    <row r="160" spans="9:9" ht="15.75" thickBot="1">
+    <row r="160" spans="9:9" ht="15" thickBot="1">
       <c r="I160" s="46"/>
     </row>
-    <row r="161" spans="9:9" ht="15.75" thickBot="1">
+    <row r="161" spans="9:9" ht="15" thickBot="1">
       <c r="I161" s="46"/>
     </row>
-    <row r="162" spans="9:9" ht="15.75" thickBot="1">
+    <row r="162" spans="9:9" ht="15" thickBot="1">
       <c r="I162" s="46"/>
     </row>
-    <row r="163" spans="9:9" ht="15.75" thickBot="1">
+    <row r="163" spans="9:9" ht="15" thickBot="1">
       <c r="I163" s="46"/>
     </row>
-    <row r="164" spans="9:9" ht="15.75" thickBot="1">
+    <row r="164" spans="9:9" ht="15" thickBot="1">
       <c r="I164" s="46"/>
     </row>
-    <row r="165" spans="9:9" ht="15.75" thickBot="1">
+    <row r="165" spans="9:9" ht="15" thickBot="1">
       <c r="I165" s="46"/>
     </row>
-    <row r="166" spans="9:9" ht="15.75" thickBot="1">
+    <row r="166" spans="9:9" ht="15" thickBot="1">
       <c r="I166" s="46"/>
     </row>
-    <row r="167" spans="9:9" ht="15.75" thickBot="1">
+    <row r="167" spans="9:9" ht="15" thickBot="1">
       <c r="I167" s="46"/>
     </row>
-    <row r="168" spans="9:9" ht="15.75" thickBot="1">
+    <row r="168" spans="9:9" ht="15" thickBot="1">
       <c r="I168" s="46"/>
     </row>
-    <row r="169" spans="9:9" ht="15.75" thickBot="1">
+    <row r="169" spans="9:9" ht="15" thickBot="1">
       <c r="I169" s="46"/>
     </row>
-    <row r="170" spans="9:9" ht="15.75" thickBot="1">
+    <row r="170" spans="9:9" ht="15" thickBot="1">
       <c r="I170" s="46"/>
     </row>
-    <row r="171" spans="9:9" ht="15.75" thickBot="1">
+    <row r="171" spans="9:9" ht="15" thickBot="1">
       <c r="I171" s="46"/>
     </row>
-    <row r="172" spans="9:9" ht="15.75" thickBot="1">
+    <row r="172" spans="9:9" ht="15" thickBot="1">
       <c r="I172" s="46"/>
     </row>
-    <row r="173" spans="9:9" ht="15.75" thickBot="1">
+    <row r="173" spans="9:9" ht="15" thickBot="1">
       <c r="I173" s="46"/>
     </row>
-    <row r="174" spans="9:9" ht="15.75" thickBot="1">
+    <row r="174" spans="9:9" ht="15" thickBot="1">
       <c r="I174" s="46"/>
     </row>
-    <row r="175" spans="9:9" ht="15.75" thickBot="1">
+    <row r="175" spans="9:9" ht="15" thickBot="1">
       <c r="I175" s="46"/>
     </row>
-    <row r="176" spans="9:9" ht="15.75" thickBot="1">
+    <row r="176" spans="9:9" ht="15" thickBot="1">
       <c r="I176" s="46"/>
     </row>
-    <row r="177" spans="9:9" ht="15.75" thickBot="1">
+    <row r="177" spans="9:9" ht="15" thickBot="1">
       <c r="I177" s="46"/>
     </row>
-    <row r="178" spans="9:9" ht="15.75" thickBot="1">
+    <row r="178" spans="9:9" ht="15" thickBot="1">
       <c r="I178" s="46"/>
     </row>
-    <row r="179" spans="9:9" ht="15.75" thickBot="1">
+    <row r="179" spans="9:9" ht="15" thickBot="1">
       <c r="I179" s="46"/>
     </row>
-    <row r="180" spans="9:9" ht="15.75" thickBot="1">
+    <row r="180" spans="9:9" ht="15" thickBot="1">
       <c r="I180" s="46"/>
     </row>
-    <row r="181" spans="9:9" ht="15.75" thickBot="1">
+    <row r="181" spans="9:9" ht="15" thickBot="1">
       <c r="I181" s="46"/>
     </row>
-    <row r="182" spans="9:9" ht="15.75" thickBot="1">
+    <row r="182" spans="9:9" ht="15" thickBot="1">
       <c r="I182" s="46"/>
     </row>
-    <row r="183" spans="9:9" ht="15.75" thickBot="1">
+    <row r="183" spans="9:9" ht="15" thickBot="1">
       <c r="I183" s="46"/>
     </row>
-    <row r="184" spans="9:9" ht="15.75" thickBot="1">
+    <row r="184" spans="9:9" ht="15" thickBot="1">
       <c r="I184" s="46"/>
     </row>
-    <row r="185" spans="9:9" ht="15.75" thickBot="1">
+    <row r="185" spans="9:9" ht="15" thickBot="1">
       <c r="I185" s="46"/>
     </row>
-    <row r="186" spans="9:9" ht="15.75" thickBot="1">
+    <row r="186" spans="9:9" ht="15" thickBot="1">
       <c r="I186" s="46"/>
     </row>
-    <row r="187" spans="9:9" ht="15.75" thickBot="1">
+    <row r="187" spans="9:9" ht="15" thickBot="1">
       <c r="I187" s="46"/>
     </row>
-    <row r="188" spans="9:9" ht="15.75" thickBot="1">
+    <row r="188" spans="9:9" ht="15" thickBot="1">
       <c r="I188" s="46"/>
     </row>
-    <row r="189" spans="9:9" ht="15.75" thickBot="1">
+    <row r="189" spans="9:9" ht="15" thickBot="1">
       <c r="I189" s="46"/>
     </row>
-    <row r="190" spans="9:9" ht="15.75" thickBot="1">
+    <row r="190" spans="9:9" ht="15" thickBot="1">
       <c r="I190" s="46"/>
     </row>
-    <row r="191" spans="9:9" ht="15.75" thickBot="1">
+    <row r="191" spans="9:9" ht="15" thickBot="1">
       <c r="I191" s="46"/>
     </row>
-    <row r="192" spans="9:9" ht="15.75" thickBot="1">
+    <row r="192" spans="9:9" ht="15" thickBot="1">
       <c r="I192" s="46"/>
     </row>
-    <row r="193" spans="9:9" ht="15.75" thickBot="1">
+    <row r="193" spans="9:9" ht="15" thickBot="1">
       <c r="I193" s="46"/>
     </row>
-    <row r="194" spans="9:9" ht="15.75" thickBot="1">
+    <row r="194" spans="9:9" ht="15" thickBot="1">
       <c r="I194" s="46"/>
     </row>
-    <row r="195" spans="9:9" ht="15.75" thickBot="1">
+    <row r="195" spans="9:9" ht="15" thickBot="1">
       <c r="I195" s="46"/>
     </row>
-    <row r="196" spans="9:9" ht="15.75" thickBot="1">
+    <row r="196" spans="9:9" ht="15" thickBot="1">
       <c r="I196" s="46"/>
     </row>
-    <row r="197" spans="9:9" ht="15.75" thickBot="1">
+    <row r="197" spans="9:9" ht="15" thickBot="1">
       <c r="I197" s="46"/>
     </row>
-    <row r="198" spans="9:9" ht="15.75" thickBot="1">
+    <row r="198" spans="9:9" ht="15" thickBot="1">
       <c r="I198" s="46"/>
     </row>
-    <row r="199" spans="9:9" ht="15.75" thickBot="1">
+    <row r="199" spans="9:9" ht="15" thickBot="1">
       <c r="I199" s="46"/>
     </row>
-    <row r="200" spans="9:9" ht="15.75" thickBot="1">
+    <row r="200" spans="9:9" ht="15" thickBot="1">
       <c r="I200" s="46"/>
     </row>
-    <row r="201" spans="9:9" ht="15.75" thickBot="1">
+    <row r="201" spans="9:9" ht="15" thickBot="1">
       <c r="I201" s="46"/>
     </row>
-    <row r="202" spans="9:9" ht="15.75" thickBot="1">
+    <row r="202" spans="9:9" ht="15" thickBot="1">
       <c r="I202" s="46"/>
     </row>
-    <row r="203" spans="9:9" ht="15.75" thickBot="1">
+    <row r="203" spans="9:9" ht="15" thickBot="1">
       <c r="I203" s="46"/>
     </row>
-    <row r="204" spans="9:9" ht="15.75" thickBot="1">
+    <row r="204" spans="9:9" ht="15" thickBot="1">
       <c r="I204" s="46"/>
     </row>
-    <row r="205" spans="9:9" ht="15.75" thickBot="1">
+    <row r="205" spans="9:9" ht="15" thickBot="1">
       <c r="I205" s="46"/>
     </row>
-    <row r="206" spans="9:9" ht="15.75" thickBot="1">
+    <row r="206" spans="9:9" ht="15" thickBot="1">
       <c r="I206" s="46"/>
     </row>
-    <row r="207" spans="9:9" ht="15.75" thickBot="1">
+    <row r="207" spans="9:9" ht="15" thickBot="1">
       <c r="I207" s="46"/>
     </row>
-    <row r="208" spans="9:9" ht="15.75" thickBot="1">
+    <row r="208" spans="9:9" ht="15" thickBot="1">
       <c r="I208" s="46"/>
     </row>
-    <row r="209" spans="9:9" ht="15.75" thickBot="1">
+    <row r="209" spans="9:9" ht="15" thickBot="1">
       <c r="I209" s="46"/>
     </row>
-    <row r="210" spans="9:9" ht="15.75" thickBot="1">
+    <row r="210" spans="9:9" ht="15" thickBot="1">
       <c r="I210" s="46"/>
     </row>
-    <row r="211" spans="9:9" ht="15.75" thickBot="1">
+    <row r="211" spans="9:9" ht="15" thickBot="1">
       <c r="I211" s="46"/>
     </row>
-    <row r="212" spans="9:9" ht="15.75" thickBot="1">
+    <row r="212" spans="9:9" ht="15" thickBot="1">
       <c r="I212" s="46"/>
     </row>
-    <row r="213" spans="9:9" ht="15.75" thickBot="1">
+    <row r="213" spans="9:9" ht="15" thickBot="1">
       <c r="I213" s="46"/>
     </row>
-    <row r="214" spans="9:9" ht="15.75" thickBot="1">
+    <row r="214" spans="9:9" ht="15" thickBot="1">
       <c r="I214" s="46"/>
     </row>
-    <row r="215" spans="9:9" ht="15.75" thickBot="1">
+    <row r="215" spans="9:9" ht="15" thickBot="1">
       <c r="I215" s="46"/>
     </row>
-    <row r="216" spans="9:9" ht="15.75" thickBot="1">
+    <row r="216" spans="9:9" ht="15" thickBot="1">
       <c r="I216" s="46"/>
     </row>
-    <row r="217" spans="9:9" ht="15.75" thickBot="1">
+    <row r="217" spans="9:9" ht="15" thickBot="1">
       <c r="I217" s="46"/>
     </row>
-    <row r="218" spans="9:9" ht="15.75" thickBot="1">
+    <row r="218" spans="9:9" ht="15" thickBot="1">
       <c r="I218" s="46"/>
     </row>
-    <row r="219" spans="9:9" ht="15.75" thickBot="1">
+    <row r="219" spans="9:9" ht="15" thickBot="1">
       <c r="I219" s="46"/>
     </row>
-    <row r="220" spans="9:9" ht="15.75" thickBot="1">
+    <row r="220" spans="9:9" ht="15" thickBot="1">
       <c r="I220" s="46"/>
     </row>
-    <row r="221" spans="9:9" ht="15.75" thickBot="1">
+    <row r="221" spans="9:9" ht="15" thickBot="1">
       <c r="I221" s="46"/>
     </row>
-    <row r="222" spans="9:9" ht="15.75" thickBot="1">
+    <row r="222" spans="9:9" ht="15" thickBot="1">
       <c r="I222" s="46"/>
     </row>
-    <row r="223" spans="9:9" ht="15.75" thickBot="1">
+    <row r="223" spans="9:9" ht="15" thickBot="1">
       <c r="I223" s="46"/>
     </row>
-    <row r="224" spans="9:9" ht="15.75" thickBot="1">
+    <row r="224" spans="9:9" ht="15" thickBot="1">
       <c r="I224" s="46"/>
     </row>
-    <row r="225" spans="9:9" ht="15.75" thickBot="1">
+    <row r="225" spans="9:9" ht="15" thickBot="1">
       <c r="I225" s="46"/>
     </row>
-    <row r="226" spans="9:9" ht="15.75" thickBot="1">
+    <row r="226" spans="9:9" ht="15" thickBot="1">
       <c r="I226" s="46"/>
     </row>
-    <row r="227" spans="9:9" ht="15.75" thickBot="1">
+    <row r="227" spans="9:9" ht="15" thickBot="1">
       <c r="I227" s="46"/>
     </row>
-    <row r="228" spans="9:9" ht="15.75" thickBot="1">
+    <row r="228" spans="9:9" ht="15" thickBot="1">
       <c r="I228" s="46"/>
     </row>
-    <row r="229" spans="9:9" ht="15.75" thickBot="1">
+    <row r="229" spans="9:9" ht="15" thickBot="1">
       <c r="I229" s="46"/>
     </row>
-    <row r="230" spans="9:9" ht="15.75" thickBot="1">
+    <row r="230" spans="9:9" ht="15" thickBot="1">
       <c r="I230" s="46"/>
     </row>
-    <row r="231" spans="9:9" ht="15.75" thickBot="1">
+    <row r="231" spans="9:9" ht="15" thickBot="1">
       <c r="I231" s="46"/>
     </row>
-    <row r="232" spans="9:9" ht="15.75" thickBot="1">
+    <row r="232" spans="9:9" ht="15" thickBot="1">
       <c r="I232" s="46"/>
     </row>
-    <row r="233" spans="9:9" ht="15.75" thickBot="1">
+    <row r="233" spans="9:9" ht="15" thickBot="1">
       <c r="I233" s="46"/>
     </row>
-    <row r="234" spans="9:9" ht="15.75" thickBot="1">
+    <row r="234" spans="9:9" ht="15" thickBot="1">
       <c r="I234" s="46"/>
     </row>
-    <row r="235" spans="9:9" ht="15.75" thickBot="1">
+    <row r="235" spans="9:9" ht="15" thickBot="1">
       <c r="I235" s="46"/>
     </row>
-    <row r="236" spans="9:9" ht="15.75" thickBot="1">
+    <row r="236" spans="9:9" ht="15" thickBot="1">
       <c r="I236" s="46"/>
     </row>
-    <row r="237" spans="9:9" ht="15.75" thickBot="1">
+    <row r="237" spans="9:9" ht="15" thickBot="1">
       <c r="I237" s="46"/>
     </row>
-    <row r="238" spans="9:9" ht="15.75" thickBot="1">
+    <row r="238" spans="9:9" ht="15" thickBot="1">
       <c r="I238" s="46"/>
     </row>
-    <row r="239" spans="9:9" ht="15.75" thickBot="1">
+    <row r="239" spans="9:9" ht="15" thickBot="1">
       <c r="I239" s="46"/>
     </row>
-    <row r="240" spans="9:9" ht="15.75" thickBot="1">
+    <row r="240" spans="9:9" ht="15" thickBot="1">
       <c r="I240" s="46"/>
     </row>
-    <row r="241" spans="9:9" ht="15.75" thickBot="1">
+    <row r="241" spans="9:9" ht="15" thickBot="1">
       <c r="I241" s="46"/>
     </row>
-    <row r="242" spans="9:9" ht="15.75" thickBot="1">
+    <row r="242" spans="9:9" ht="15" thickBot="1">
       <c r="I242" s="46"/>
     </row>
-    <row r="243" spans="9:9" ht="15.75" thickBot="1">
+    <row r="243" spans="9:9" ht="15" thickBot="1">
       <c r="I243" s="46"/>
     </row>
-    <row r="244" spans="9:9" ht="15.75" thickBot="1">
+    <row r="244" spans="9:9" ht="15" thickBot="1">
       <c r="I244" s="46"/>
     </row>
-    <row r="245" spans="9:9" ht="15.75" thickBot="1">
+    <row r="245" spans="9:9" ht="15" thickBot="1">
       <c r="I245" s="46"/>
     </row>
-    <row r="246" spans="9:9" ht="15.75" thickBot="1">
+    <row r="246" spans="9:9" ht="15" thickBot="1">
       <c r="I246" s="46"/>
     </row>
-    <row r="247" spans="9:9" ht="15.75" thickBot="1">
+    <row r="247" spans="9:9" ht="15" thickBot="1">
       <c r="I247" s="46"/>
     </row>
-    <row r="248" spans="9:9" ht="15.75" thickBot="1">
+    <row r="248" spans="9:9" ht="15" thickBot="1">
       <c r="I248" s="46"/>
     </row>
-    <row r="249" spans="9:9" ht="15.75" thickBot="1">
+    <row r="249" spans="9:9" ht="15" thickBot="1">
       <c r="I249" s="46"/>
     </row>
-    <row r="250" spans="9:9" ht="15.75" thickBot="1">
+    <row r="250" spans="9:9" ht="15" thickBot="1">
       <c r="I250" s="46"/>
     </row>
-    <row r="251" spans="9:9" ht="15.75" thickBot="1">
+    <row r="251" spans="9:9" ht="15" thickBot="1">
       <c r="I251" s="46"/>
     </row>
-    <row r="252" spans="9:9" ht="15.75" thickBot="1">
+    <row r="252" spans="9:9" ht="15" thickBot="1">
       <c r="I252" s="46"/>
     </row>
-    <row r="253" spans="9:9" ht="15.75" thickBot="1">
+    <row r="253" spans="9:9" ht="15" thickBot="1">
       <c r="I253" s="46"/>
     </row>
-    <row r="254" spans="9:9" ht="15.75" thickBot="1">
+    <row r="254" spans="9:9" ht="15" thickBot="1">
       <c r="I254" s="46"/>
     </row>
-    <row r="255" spans="9:9" ht="15.75" thickBot="1">
+    <row r="255" spans="9:9" ht="15" thickBot="1">
       <c r="I255" s="46"/>
     </row>
-    <row r="256" spans="9:9" ht="15.75" thickBot="1">
+    <row r="256" spans="9:9" ht="15" thickBot="1">
       <c r="I256" s="46"/>
     </row>
-    <row r="257" spans="9:9" ht="15.75" thickBot="1">
+    <row r="257" spans="9:9" ht="15" thickBot="1">
       <c r="I257" s="46"/>
     </row>
-    <row r="258" spans="9:9" ht="15.75" thickBot="1">
+    <row r="258" spans="9:9" ht="15" thickBot="1">
       <c r="I258" s="46"/>
     </row>
-    <row r="259" spans="9:9" ht="15.75" thickBot="1">
+    <row r="259" spans="9:9" ht="15" thickBot="1">
       <c r="I259" s="46"/>
     </row>
-    <row r="260" spans="9:9" ht="15.75" thickBot="1">
+    <row r="260" spans="9:9" ht="15" thickBot="1">
       <c r="I260" s="46"/>
     </row>
-    <row r="261" spans="9:9" ht="15.75" thickBot="1">
+    <row r="261" spans="9:9" ht="15" thickBot="1">
       <c r="I261" s="46"/>
     </row>
-    <row r="262" spans="9:9" ht="15.75" thickBot="1">
+    <row r="262" spans="9:9" ht="15" thickBot="1">
       <c r="I262" s="46"/>
     </row>
-    <row r="263" spans="9:9" ht="15.75" thickBot="1">
+    <row r="263" spans="9:9" ht="15" thickBot="1">
       <c r="I263" s="46"/>
     </row>
-    <row r="264" spans="9:9" ht="15.75" thickBot="1">
+    <row r="264" spans="9:9" ht="15" thickBot="1">
       <c r="I264" s="46"/>
     </row>
-    <row r="265" spans="9:9" ht="15.75" thickBot="1">
+    <row r="265" spans="9:9" ht="15" thickBot="1">
       <c r="I265" s="46"/>
     </row>
-    <row r="266" spans="9:9" ht="15.75" thickBot="1">
+    <row r="266" spans="9:9" ht="15" thickBot="1">
       <c r="I266" s="46"/>
     </row>
-    <row r="267" spans="9:9" ht="15.75" thickBot="1">
+    <row r="267" spans="9:9" ht="15" thickBot="1">
       <c r="I267" s="46"/>
     </row>
-    <row r="268" spans="9:9" ht="15.75" thickBot="1">
+    <row r="268" spans="9:9" ht="15" thickBot="1">
       <c r="I268" s="46"/>
     </row>
-    <row r="269" spans="9:9" ht="15.75" thickBot="1">
+    <row r="269" spans="9:9" ht="15" thickBot="1">
       <c r="I269" s="46"/>
     </row>
-    <row r="270" spans="9:9" ht="15.75" thickBot="1">
+    <row r="270" spans="9:9" ht="15" thickBot="1">
       <c r="I270" s="46"/>
     </row>
-    <row r="271" spans="9:9" ht="15.75" thickBot="1">
+    <row r="271" spans="9:9" ht="15" thickBot="1">
       <c r="I271" s="46"/>
     </row>
-    <row r="272" spans="9:9" ht="15.75" thickBot="1">
+    <row r="272" spans="9:9" ht="15" thickBot="1">
       <c r="I272" s="46"/>
     </row>
-    <row r="273" spans="9:9" ht="15.75" thickBot="1">
+    <row r="273" spans="9:9" ht="15" thickBot="1">
       <c r="I273" s="46"/>
     </row>
-    <row r="274" spans="9:9" ht="15.75" thickBot="1">
+    <row r="274" spans="9:9" ht="15" thickBot="1">
       <c r="I274" s="46"/>
     </row>
-    <row r="275" spans="9:9" ht="15.75" thickBot="1">
+    <row r="275" spans="9:9" ht="15" thickBot="1">
       <c r="I275" s="46"/>
     </row>
-    <row r="276" spans="9:9" ht="15.75" thickBot="1">
+    <row r="276" spans="9:9" ht="15" thickBot="1">
       <c r="I276" s="46"/>
     </row>
-    <row r="277" spans="9:9" ht="15.75" thickBot="1">
+    <row r="277" spans="9:9" ht="15" thickBot="1">
       <c r="I277" s="46"/>
     </row>
-    <row r="278" spans="9:9" ht="15.75" thickBot="1">
+    <row r="278" spans="9:9" ht="15" thickBot="1">
       <c r="I278" s="46"/>
     </row>
-    <row r="279" spans="9:9" ht="15.75" thickBot="1">
+    <row r="279" spans="9:9" ht="15" thickBot="1">
       <c r="I279" s="46"/>
     </row>
-    <row r="280" spans="9:9" ht="15.75" thickBot="1">
+    <row r="280" spans="9:9" ht="15" thickBot="1">
       <c r="I280" s="46"/>
     </row>
-    <row r="281" spans="9:9" ht="15.75" thickBot="1">
+    <row r="281" spans="9:9" ht="15" thickBot="1">
       <c r="I281" s="46"/>
     </row>
-    <row r="282" spans="9:9" ht="15.75" thickBot="1">
+    <row r="282" spans="9:9" ht="15" thickBot="1">
       <c r="I282" s="46"/>
     </row>
-    <row r="283" spans="9:9" ht="15.75" thickBot="1">
+    <row r="283" spans="9:9" ht="15" thickBot="1">
       <c r="I283" s="46"/>
     </row>
-    <row r="284" spans="9:9" ht="15.75" thickBot="1">
+    <row r="284" spans="9:9" ht="15" thickBot="1">
       <c r="I284" s="46"/>
     </row>
-    <row r="285" spans="9:9" ht="15.75" thickBot="1">
+    <row r="285" spans="9:9" ht="15" thickBot="1">
       <c r="I285" s="46"/>
     </row>
-    <row r="286" spans="9:9" ht="15.75" thickBot="1">
+    <row r="286" spans="9:9" ht="15" thickBot="1">
       <c r="I286" s="46"/>
     </row>
-    <row r="287" spans="9:9" ht="15.75" thickBot="1">
+    <row r="287" spans="9:9" ht="15" thickBot="1">
       <c r="I287" s="46"/>
     </row>
-    <row r="288" spans="9:9" ht="15.75" thickBot="1">
+    <row r="288" spans="9:9" ht="15" thickBot="1">
       <c r="I288" s="46"/>
     </row>
-    <row r="289" spans="9:9" ht="15.75" thickBot="1">
+    <row r="289" spans="9:9" ht="15" thickBot="1">
       <c r="I289" s="46"/>
     </row>
-    <row r="290" spans="9:9" ht="15.75" thickBot="1">
+    <row r="290" spans="9:9" ht="15" thickBot="1">
       <c r="I290" s="46"/>
     </row>
-    <row r="291" spans="9:9" ht="15.75" thickBot="1">
+    <row r="291" spans="9:9" ht="15" thickBot="1">
       <c r="I291" s="46"/>
     </row>
-    <row r="292" spans="9:9" ht="15.75" thickBot="1">
+    <row r="292" spans="9:9" ht="15" thickBot="1">
       <c r="I292" s="46"/>
     </row>
-    <row r="293" spans="9:9" ht="15.75" thickBot="1">
+    <row r="293" spans="9:9" ht="15" thickBot="1">
       <c r="I293" s="46"/>
     </row>
-    <row r="294" spans="9:9" ht="15.75" thickBot="1">
+    <row r="294" spans="9:9" ht="15" thickBot="1">
       <c r="I294" s="46"/>
     </row>
-    <row r="295" spans="9:9" ht="15.75" thickBot="1">
+    <row r="295" spans="9:9" ht="15" thickBot="1">
       <c r="I295" s="46"/>
     </row>
-    <row r="296" spans="9:9" ht="15.75" thickBot="1">
+    <row r="296" spans="9:9" ht="15" thickBot="1">
       <c r="I296" s="46"/>
     </row>
-    <row r="297" spans="9:9" ht="15.75" thickBot="1">
+    <row r="297" spans="9:9" ht="15" thickBot="1">
       <c r="I297" s="39"/>
     </row>
-    <row r="298" spans="9:9" ht="15.75" thickBot="1">
+    <row r="298" spans="9:9" ht="15" thickBot="1">
       <c r="I298" s="21" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="299" spans="9:9" ht="15.75" thickBot="1">
+    <row r="299" spans="9:9" ht="15" thickBot="1">
       <c r="I299" s="21" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="300" spans="9:9" ht="15" thickBot="1">
+    <row r="300" spans="9:9" ht="14.4" thickBot="1">
       <c r="I300" s="36" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="301" spans="9:9" ht="15" thickBot="1">
+    <row r="301" spans="9:9" ht="14.4" thickBot="1">
       <c r="I301" s="36" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="302" spans="9:9" ht="15" thickBot="1">
+    <row r="302" spans="9:9" ht="14.4" thickBot="1">
       <c r="I302" s="36" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="303" spans="9:9" ht="15" thickBot="1">
+    <row r="303" spans="9:9" ht="14.4" thickBot="1">
       <c r="I303" s="36" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="304" spans="9:9" ht="15" thickBot="1">
+    <row r="304" spans="9:9" ht="14.4" thickBot="1">
       <c r="I304" s="36" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="305" spans="9:9" ht="15" thickBot="1">
+    <row r="305" spans="9:9" ht="14.4" thickBot="1">
       <c r="I305" s="36" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="306" spans="9:9" ht="15.75" thickBot="1">
+    <row r="306" spans="9:9" ht="15" thickBot="1">
       <c r="I306" s="21" t="s">
         <v>553</v>
       </c>
@@ -10576,31 +10579,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D011BDFC-04A7-4A03-9396-91A8DE874C29}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:W4549"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.375" customWidth="1"/>
-    <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.75" customWidth="1"/>
-    <col min="9" max="9" width="15.875" customWidth="1"/>
-    <col min="10" max="10" width="12.75" customWidth="1"/>
+    <col min="2" max="2" width="26.3984375" customWidth="1"/>
+    <col min="3" max="3" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.69921875" customWidth="1"/>
+    <col min="9" max="9" width="15.8984375" customWidth="1"/>
+    <col min="10" max="10" width="12.69921875" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.375" customWidth="1"/>
+    <col min="12" max="12" width="16.3984375" customWidth="1"/>
     <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.19921875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" customWidth="1"/>
-    <col min="16" max="16" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.375" customWidth="1"/>
-    <col min="20" max="20" width="59.125" customWidth="1"/>
-    <col min="21" max="21" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.3984375" customWidth="1"/>
+    <col min="20" max="20" width="59.09765625" customWidth="1"/>
+    <col min="21" max="21" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="2" customFormat="1" ht="15">
+    <row r="1" spans="1:23" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>190</v>
       </c>
@@ -48287,42 +48290,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D227756-72D6-431F-A8FB-E1CD23651F85}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:AA155"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.25" customWidth="1"/>
-    <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.19921875" customWidth="1"/>
+    <col min="5" max="5" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.09765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.69921875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.25" customWidth="1"/>
+    <col min="13" max="13" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.19921875" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.375" customWidth="1"/>
-    <col min="23" max="23" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.3984375" customWidth="1"/>
+    <col min="23" max="23" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.69921875" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="16" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.69921875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="2" customFormat="1" ht="15">
+    <row r="1" spans="1:27" s="2" customFormat="1" ht="14.4">
       <c r="A1" s="2" t="s">
         <v>190</v>
       </c>
@@ -49340,21 +49343,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9AAF5DE-78EF-42C9-9FE8-41208EDCE960}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:AF298"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.375" customWidth="1"/>
-    <col min="5" max="5" width="19.25" customWidth="1"/>
-    <col min="6" max="6" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.75" customWidth="1"/>
-    <col min="19" max="19" width="51.875" customWidth="1"/>
-    <col min="20" max="20" width="29.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.3984375" customWidth="1"/>
+    <col min="5" max="5" width="19.19921875" customWidth="1"/>
+    <col min="6" max="6" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.69921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.69921875" customWidth="1"/>
+    <col min="19" max="19" width="51.8984375" customWidth="1"/>
+    <col min="20" max="20" width="29.3984375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15">
+    <row r="1" spans="1:32">
       <c r="A1" s="2" t="s">
         <v>190</v>
       </c>
@@ -49415,7 +49419,9 @@
       <c r="T1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="U1" s="2"/>
+      <c r="U1" s="2" t="s">
+        <v>800</v>
+      </c>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
@@ -49893,7 +49899,7 @@
         <v xml:space="preserve">SSD, Portable_Storage, </v>
       </c>
     </row>
-    <row r="15" spans="1:32" ht="15">
+    <row r="15" spans="1:32">
       <c r="A15">
         <v>14</v>
       </c>
